--- a/ISMS/Security_Encryption_Methods.xlsx
+++ b/ISMS/Security_Encryption_Methods.xlsx
@@ -3,37 +3,34 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D489A77-6776-4DCC-BBA1-B9709EFA2D21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C7AEF1-F237-4A55-8A4A-86452A37A568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="867" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="928" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Version" sheetId="10" r:id="rId1"/>
     <sheet name="Summary" sheetId="1" r:id="rId2"/>
-    <sheet name="AWS Account Mgmt" sheetId="2" r:id="rId3"/>
-    <sheet name="AWS Instance Connection" sheetId="3" r:id="rId4"/>
-    <sheet name="SFTP,SCP,SCP using Key,VSFTP" sheetId="4" r:id="rId5"/>
-    <sheet name="Https" sheetId="5" r:id="rId6"/>
-    <sheet name="Oauth" sheetId="6" r:id="rId7"/>
-    <sheet name="Encryption" sheetId="7" r:id="rId8"/>
-    <sheet name="VPN" sheetId="11" r:id="rId9"/>
-    <sheet name="2FA" sheetId="12" r:id="rId10"/>
-    <sheet name="Password" sheetId="13" r:id="rId11"/>
-    <sheet name="Application Security" sheetId="14" r:id="rId12"/>
+    <sheet name="Application Data Security" sheetId="14" r:id="rId3"/>
+    <sheet name="AWS Account Mgmt" sheetId="2" r:id="rId4"/>
+    <sheet name="AWS Instance Connection" sheetId="3" r:id="rId5"/>
+    <sheet name="SFTP,SCP,SCP using Key,VSFTP" sheetId="4" r:id="rId6"/>
+    <sheet name="Https" sheetId="5" r:id="rId7"/>
+    <sheet name="Oauth" sheetId="6" r:id="rId8"/>
+    <sheet name="Encryption" sheetId="7" r:id="rId9"/>
+    <sheet name="VPN" sheetId="11" r:id="rId10"/>
+    <sheet name="2FA" sheetId="12" r:id="rId11"/>
+    <sheet name="Password" sheetId="13" r:id="rId12"/>
   </sheets>
   <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="328">
   <si>
     <t>System</t>
   </si>
   <si>
-    <t>Document</t>
-  </si>
-  <si>
     <t>By</t>
   </si>
   <si>
@@ -47,9 +44,6 @@
   </si>
   <si>
     <t>Summary</t>
-  </si>
-  <si>
-    <t>Security and Encryption</t>
   </si>
   <si>
     <t>Common</t>
@@ -1570,9 +1564,6 @@
     <t>2FA protects against phishing, social engineering and password brute-force attacks and secures your logins from attackers exploiting weak or stolen credentials</t>
   </si>
   <si>
-    <t>we are using 2FA for AWS account login.</t>
-  </si>
-  <si>
     <t>12 characters ‍</t>
   </si>
   <si>
@@ -2333,9 +2324,6 @@
     </r>
   </si>
   <si>
-    <t>Application Security</t>
-  </si>
-  <si>
     <r>
       <t>✅ S</t>
     </r>
@@ -2390,6 +2378,60 @@
   </si>
   <si>
     <t>box.com</t>
+  </si>
+  <si>
+    <t>Security and Encryption for Data</t>
+  </si>
+  <si>
+    <t>Summary Document</t>
+  </si>
+  <si>
+    <t>Application Data Security</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">6. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Compress and set a password on Excel files containing sensitive data.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">✅  Set API </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rate limits</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to prevent abuse and denial-of-service attacks.</t>
+    </r>
+  </si>
+  <si>
+    <t>✅ Always segregate credentials between environments to prevent data leaks and unauthorized access.</t>
   </si>
 </sst>
 </file>
@@ -2399,9 +2441,9 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yyyy;@"/>
-    <numFmt numFmtId="167" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="166" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2608,6 +2650,12 @@
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -2647,7 +2695,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -2937,6 +2985,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2947,7 +3004,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="2"/>
@@ -3064,6 +3121,37 @@
     <xf numFmtId="164" fontId="24" fillId="0" borderId="22" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="22" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="22" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3088,84 +3176,72 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="165" fontId="24" fillId="0" borderId="22" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="24" fillId="0" borderId="24" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3178,24 +3254,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="22" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="23" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="24" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3214,18 +3302,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3244,24 +3332,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="24" fillId="0" borderId="22" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="24" fillId="0" borderId="24" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="22" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="23" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="24" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="24" fillId="0" borderId="22" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3277,33 +3347,30 @@
     <xf numFmtId="164" fontId="24" fillId="0" borderId="24" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="22" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="22" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -3621,8 +3688,8 @@
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>28232</xdr:colOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>237782</xdr:colOff>
       <xdr:row>27</xdr:row>
       <xdr:rowOff>171396</xdr:rowOff>
     </xdr:to>
@@ -3719,8 +3786,8 @@
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>5477782</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>429532</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>180975</xdr:rowOff>
     </xdr:to>
@@ -3763,8 +3830,8 @@
       <xdr:rowOff>123826</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>5343525</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>180975</xdr:rowOff>
     </xdr:to>
@@ -3812,8 +3879,8 @@
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>115588</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>20338</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>66997</xdr:rowOff>
     </xdr:to>
@@ -4147,225 +4214,225 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="54" t="s">
-        <v>258</v>
-      </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
+      <c r="A1" s="65" t="s">
+        <v>255</v>
+      </c>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
     </row>
     <row r="3" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A3" s="58"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
+      <c r="A3" s="69"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="70"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="31"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="60" t="s">
-        <v>207</v>
-      </c>
-      <c r="B5" s="61"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
+      <c r="A5" s="71" t="s">
+        <v>205</v>
+      </c>
+      <c r="B5" s="72"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="31"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="62"/>
-      <c r="B7" s="63" t="s">
-        <v>208</v>
-      </c>
-      <c r="C7" s="63"/>
-      <c r="D7" s="63"/>
-      <c r="E7" s="63"/>
-      <c r="F7" s="63"/>
-      <c r="G7" s="63"/>
-      <c r="H7" s="63"/>
+      <c r="A7" s="63"/>
+      <c r="B7" s="64" t="s">
+        <v>206</v>
+      </c>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="64"/>
+      <c r="H7" s="64"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="62"/>
-      <c r="B8" s="64" t="s">
-        <v>213</v>
-      </c>
-      <c r="C8" s="64"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
+      <c r="A8" s="63"/>
+      <c r="B8" s="73" t="s">
+        <v>211</v>
+      </c>
+      <c r="C8" s="73"/>
+      <c r="D8" s="73"/>
+      <c r="E8" s="73"/>
+      <c r="F8" s="73"/>
+      <c r="G8" s="73"/>
+      <c r="H8" s="73"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="62"/>
-      <c r="B9" s="64"/>
-      <c r="C9" s="64"/>
-      <c r="D9" s="64"/>
-      <c r="E9" s="64"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="64"/>
-      <c r="H9" s="64"/>
+      <c r="A9" s="63"/>
+      <c r="B9" s="73"/>
+      <c r="C9" s="73"/>
+      <c r="D9" s="73"/>
+      <c r="E9" s="73"/>
+      <c r="F9" s="73"/>
+      <c r="G9" s="73"/>
+      <c r="H9" s="73"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="31"/>
     </row>
     <row r="11" spans="1:8" ht="24">
       <c r="A11" s="32" t="s">
+        <v>207</v>
+      </c>
+      <c r="B11" s="33" t="s">
+        <v>208</v>
+      </c>
+      <c r="C11" s="33" t="s">
         <v>209</v>
       </c>
-      <c r="B11" s="33" t="s">
-        <v>210</v>
-      </c>
-      <c r="C11" s="33" t="s">
-        <v>211</v>
-      </c>
       <c r="D11" s="33" t="s">
-        <v>214</v>
-      </c>
-      <c r="E11" s="65" t="s">
-        <v>215</v>
-      </c>
-      <c r="F11" s="66"/>
-      <c r="G11" s="66"/>
-      <c r="H11" s="66"/>
+        <v>212</v>
+      </c>
+      <c r="E11" s="58" t="s">
+        <v>213</v>
+      </c>
+      <c r="F11" s="59"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="59"/>
     </row>
     <row r="12" spans="1:8" ht="15.75">
       <c r="A12" s="37"/>
       <c r="B12" s="38"/>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="68"/>
-      <c r="G12" s="68"/>
-      <c r="H12" s="69"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="62"/>
     </row>
     <row r="13" spans="1:8" ht="15.75">
       <c r="A13" s="37"/>
       <c r="B13" s="38"/>
       <c r="C13" s="8"/>
       <c r="D13" s="46"/>
-      <c r="E13" s="67"/>
-      <c r="F13" s="68"/>
-      <c r="G13" s="68"/>
-      <c r="H13" s="69"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="61"/>
+      <c r="G13" s="61"/>
+      <c r="H13" s="62"/>
     </row>
     <row r="14" spans="1:8" ht="15.75">
       <c r="A14" s="37"/>
       <c r="B14" s="38"/>
       <c r="C14" s="8"/>
       <c r="D14" s="46"/>
-      <c r="E14" s="67"/>
-      <c r="F14" s="68"/>
-      <c r="G14" s="68"/>
-      <c r="H14" s="69"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="61"/>
+      <c r="G14" s="61"/>
+      <c r="H14" s="62"/>
     </row>
     <row r="15" spans="1:8" ht="15.75">
       <c r="A15" s="39"/>
       <c r="B15" s="40"/>
       <c r="C15" s="8"/>
       <c r="D15" s="41"/>
-      <c r="E15" s="67"/>
-      <c r="F15" s="68"/>
-      <c r="G15" s="68"/>
-      <c r="H15" s="69"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="61"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="62"/>
     </row>
     <row r="16" spans="1:8" ht="15.75">
       <c r="A16" s="39"/>
       <c r="B16" s="40"/>
       <c r="C16" s="8"/>
       <c r="D16" s="41"/>
-      <c r="E16" s="67"/>
-      <c r="F16" s="68"/>
-      <c r="G16" s="68"/>
-      <c r="H16" s="69"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="61"/>
+      <c r="G16" s="61"/>
+      <c r="H16" s="62"/>
     </row>
     <row r="17" spans="1:8" ht="15.75">
       <c r="A17" s="42"/>
       <c r="B17" s="43"/>
       <c r="C17" s="8"/>
       <c r="D17" s="44"/>
-      <c r="E17" s="67"/>
-      <c r="F17" s="68"/>
-      <c r="G17" s="68"/>
-      <c r="H17" s="69"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="61"/>
+      <c r="G17" s="61"/>
+      <c r="H17" s="62"/>
     </row>
     <row r="18" spans="1:8" ht="15.75">
       <c r="A18" s="39"/>
       <c r="B18" s="40"/>
       <c r="C18" s="8"/>
       <c r="D18" s="41"/>
-      <c r="E18" s="67"/>
-      <c r="F18" s="68"/>
-      <c r="G18" s="68"/>
-      <c r="H18" s="69"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="61"/>
+      <c r="G18" s="61"/>
+      <c r="H18" s="62"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="34"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
-      <c r="E19" s="67"/>
-      <c r="F19" s="68"/>
-      <c r="G19" s="68"/>
-      <c r="H19" s="69"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="61"/>
+      <c r="G19" s="61"/>
+      <c r="H19" s="62"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="34"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
-      <c r="E20" s="67"/>
-      <c r="F20" s="68"/>
-      <c r="G20" s="68"/>
-      <c r="H20" s="69"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="61"/>
+      <c r="G20" s="61"/>
+      <c r="H20" s="62"/>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="62"/>
-      <c r="B21" s="63" t="s">
-        <v>264</v>
-      </c>
-      <c r="C21" s="63"/>
-      <c r="D21" s="63"/>
-      <c r="E21" s="63"/>
-      <c r="F21" s="63"/>
-      <c r="G21" s="63"/>
-      <c r="H21" s="63"/>
+      <c r="A21" s="63"/>
+      <c r="B21" s="64" t="s">
+        <v>261</v>
+      </c>
+      <c r="C21" s="64"/>
+      <c r="D21" s="64"/>
+      <c r="E21" s="64"/>
+      <c r="F21" s="64"/>
+      <c r="G21" s="64"/>
+      <c r="H21" s="64"/>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="62"/>
-      <c r="B22" s="63" t="s">
-        <v>263</v>
-      </c>
-      <c r="C22" s="63"/>
-      <c r="D22" s="63"/>
-      <c r="E22" s="63"/>
-      <c r="F22" s="63"/>
-      <c r="G22" s="63"/>
-      <c r="H22" s="63"/>
+      <c r="A22" s="63"/>
+      <c r="B22" s="64" t="s">
+        <v>260</v>
+      </c>
+      <c r="C22" s="64"/>
+      <c r="D22" s="64"/>
+      <c r="E22" s="64"/>
+      <c r="F22" s="64"/>
+      <c r="G22" s="64"/>
+      <c r="H22" s="64"/>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="31"/>
@@ -4382,6 +4449,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A1:H3"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="B8:H9"/>
     <mergeCell ref="E11:H11"/>
     <mergeCell ref="E20:H20"/>
     <mergeCell ref="A21:A22"/>
@@ -4395,11 +4467,6 @@
     <mergeCell ref="E16:H16"/>
     <mergeCell ref="E17:H17"/>
     <mergeCell ref="E18:H18"/>
-    <mergeCell ref="A1:H3"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="B8:H9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -4411,200 +4478,369 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:R37"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="16" max="16" width="4.5703125" customWidth="1"/>
+    <col min="17" max="17" width="6" customWidth="1"/>
+    <col min="18" max="18" width="4.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="15.75" thickBot="1">
+      <c r="A1" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="99" t="s">
+        <v>217</v>
+      </c>
+      <c r="C1" s="100"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="125" t="s">
+        <v>256</v>
+      </c>
+      <c r="F1" s="126"/>
+      <c r="G1" s="99" t="s">
+        <v>218</v>
+      </c>
+      <c r="H1" s="100"/>
+      <c r="I1" s="100"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="86" t="s">
+        <v>210</v>
+      </c>
+      <c r="L1" s="127"/>
+      <c r="M1" s="87"/>
+      <c r="N1" s="99" t="s">
+        <v>219</v>
+      </c>
+      <c r="O1" s="101"/>
+      <c r="P1" s="85">
+        <v>45931</v>
+      </c>
+      <c r="Q1" s="85"/>
+      <c r="R1" s="85"/>
+    </row>
+    <row r="2" spans="1:18" ht="15.75" thickBot="1">
+      <c r="B2" s="99" t="s">
+        <v>220</v>
+      </c>
+      <c r="C2" s="100"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="128">
+        <v>0</v>
+      </c>
+      <c r="F2" s="129"/>
+      <c r="G2" s="99" t="s">
+        <v>221</v>
+      </c>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="101"/>
+      <c r="K2" s="86" t="s">
+        <v>210</v>
+      </c>
+      <c r="L2" s="127"/>
+      <c r="M2" s="87"/>
+      <c r="N2" s="99" t="s">
+        <v>222</v>
+      </c>
+      <c r="O2" s="101"/>
+      <c r="P2" s="85">
+        <v>45968</v>
+      </c>
+      <c r="Q2" s="85"/>
+      <c r="R2" s="85"/>
+    </row>
+    <row r="4" spans="1:18">
+      <c r="B4" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="B5" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="B6" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3">
+      <c r="C24" s="12"/>
+    </row>
+    <row r="25" spans="2:3">
+      <c r="B25" t="s">
+        <v>224</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3">
+      <c r="C26" s="12" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3">
+      <c r="C28" s="45" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3">
+      <c r="C29" s="45" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3">
+      <c r="C30" s="45"/>
+    </row>
+    <row r="31" spans="2:3">
+      <c r="C31" s="45" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3">
+      <c r="C32" s="45"/>
+    </row>
+    <row r="33" spans="3:3">
+      <c r="C33" s="45" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="34" spans="3:3">
+      <c r="C34" s="45"/>
+    </row>
+    <row r="35" spans="3:3">
+      <c r="C35" s="45" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="36" spans="3:3">
+      <c r="C36" s="45"/>
+    </row>
+    <row r="37" spans="3:3">
+      <c r="C37" s="45"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P1:R1"/>
+    <mergeCell ref="P2:R2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C25" r:id="rId1" xr:uid="{00000000-0004-0000-0800-000000000000}"/>
+    <hyperlink ref="C26" r:id="rId2" xr:uid="{00000000-0004-0000-0800-000001000000}"/>
+    <hyperlink ref="A1" location="Summary!A1" display="Summary" xr:uid="{00000000-0004-0000-0800-000004000000}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
+  <drawing r:id="rId4"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:AE10"/>
+  <dimension ref="A1:AE8"/>
   <sheetFormatPr defaultColWidth="5.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7" customWidth="1"/>
+    <col min="17" max="17" width="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="15.75" thickBot="1">
       <c r="A1" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="117" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="99" t="s">
+        <v>217</v>
+      </c>
+      <c r="C1" s="100"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="125" t="s">
+        <v>235</v>
+      </c>
+      <c r="F1" s="126"/>
+      <c r="G1" s="99" t="s">
+        <v>218</v>
+      </c>
+      <c r="H1" s="100"/>
+      <c r="I1" s="100"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="86" t="s">
+        <v>210</v>
+      </c>
+      <c r="L1" s="127"/>
+      <c r="M1" s="87"/>
+      <c r="N1" s="99" t="s">
         <v>219</v>
       </c>
-      <c r="C1" s="118"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="120" t="s">
-        <v>237</v>
-      </c>
-      <c r="F1" s="121"/>
-      <c r="G1" s="117" t="s">
+      <c r="O1" s="101"/>
+      <c r="P1" s="85">
+        <v>45931</v>
+      </c>
+      <c r="Q1" s="85"/>
+      <c r="R1" s="85"/>
+    </row>
+    <row r="2" spans="1:31" ht="15.75" thickBot="1">
+      <c r="B2" s="99" t="s">
         <v>220</v>
       </c>
-      <c r="H1" s="118"/>
-      <c r="I1" s="118"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="115" t="s">
-        <v>212</v>
-      </c>
-      <c r="L1" s="122"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="117" t="s">
+      <c r="C2" s="100"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="128">
+        <v>1.3</v>
+      </c>
+      <c r="F2" s="129"/>
+      <c r="G2" s="99" t="s">
         <v>221</v>
       </c>
-      <c r="O1" s="119"/>
-      <c r="P1" s="115">
-        <v>45914</v>
-      </c>
-      <c r="Q1" s="116"/>
-    </row>
-    <row r="2" spans="1:31" ht="15.75" thickBot="1">
-      <c r="B2" s="117" t="s">
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="101"/>
+      <c r="K2" s="86" t="s">
+        <v>210</v>
+      </c>
+      <c r="L2" s="127"/>
+      <c r="M2" s="87"/>
+      <c r="N2" s="99" t="s">
         <v>222</v>
       </c>
-      <c r="C2" s="118"/>
-      <c r="D2" s="119"/>
-      <c r="E2" s="123">
-        <v>1.3</v>
-      </c>
-      <c r="F2" s="124"/>
-      <c r="G2" s="117" t="s">
-        <v>223</v>
-      </c>
-      <c r="H2" s="118"/>
-      <c r="I2" s="118"/>
-      <c r="J2" s="119"/>
-      <c r="K2" s="115" t="s">
-        <v>212</v>
-      </c>
-      <c r="L2" s="122"/>
-      <c r="M2" s="116"/>
-      <c r="N2" s="117" t="s">
-        <v>224</v>
-      </c>
-      <c r="O2" s="119"/>
-      <c r="P2" s="115">
-        <v>45914</v>
-      </c>
-      <c r="Q2" s="116"/>
+      <c r="O2" s="101"/>
+      <c r="P2" s="85">
+        <v>45968</v>
+      </c>
+      <c r="Q2" s="85"/>
+      <c r="R2" s="85"/>
     </row>
     <row r="4" spans="1:31" ht="14.45" customHeight="1">
-      <c r="B4" s="96" t="s">
-        <v>238</v>
-      </c>
-      <c r="C4" s="96"/>
-      <c r="D4" s="96"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="96"/>
-      <c r="G4" s="96"/>
-      <c r="H4" s="96"/>
-      <c r="I4" s="96"/>
-      <c r="J4" s="96"/>
-      <c r="K4" s="96"/>
-      <c r="L4" s="96"/>
-      <c r="M4" s="96"/>
-      <c r="N4" s="96"/>
-      <c r="O4" s="96"/>
-      <c r="P4" s="96"/>
-      <c r="Q4" s="96"/>
-      <c r="R4" s="96"/>
-      <c r="S4" s="96"/>
-      <c r="T4" s="96"/>
-      <c r="U4" s="96"/>
-      <c r="V4" s="96"/>
-      <c r="W4" s="96"/>
-      <c r="X4" s="96"/>
-      <c r="Y4" s="96"/>
-      <c r="Z4" s="96"/>
-      <c r="AA4" s="96"/>
-      <c r="AB4" s="96"/>
-      <c r="AC4" s="96"/>
-      <c r="AD4" s="96"/>
-      <c r="AE4" s="96"/>
+      <c r="B4" s="102" t="s">
+        <v>236</v>
+      </c>
+      <c r="C4" s="102"/>
+      <c r="D4" s="102"/>
+      <c r="E4" s="102"/>
+      <c r="F4" s="102"/>
+      <c r="G4" s="102"/>
+      <c r="H4" s="102"/>
+      <c r="I4" s="102"/>
+      <c r="J4" s="102"/>
+      <c r="K4" s="102"/>
+      <c r="L4" s="102"/>
+      <c r="M4" s="102"/>
+      <c r="N4" s="102"/>
+      <c r="O4" s="102"/>
+      <c r="P4" s="102"/>
+      <c r="Q4" s="102"/>
+      <c r="R4" s="102"/>
+      <c r="S4" s="102"/>
+      <c r="T4" s="102"/>
+      <c r="U4" s="102"/>
+      <c r="V4" s="102"/>
+      <c r="W4" s="102"/>
+      <c r="X4" s="102"/>
+      <c r="Y4" s="102"/>
+      <c r="Z4" s="102"/>
+      <c r="AA4" s="102"/>
+      <c r="AB4" s="102"/>
+      <c r="AC4" s="102"/>
+      <c r="AD4" s="102"/>
+      <c r="AE4" s="102"/>
     </row>
     <row r="5" spans="1:31">
-      <c r="B5" s="96"/>
-      <c r="C5" s="96"/>
-      <c r="D5" s="96"/>
-      <c r="E5" s="96"/>
-      <c r="F5" s="96"/>
-      <c r="G5" s="96"/>
-      <c r="H5" s="96"/>
-      <c r="I5" s="96"/>
-      <c r="J5" s="96"/>
-      <c r="K5" s="96"/>
-      <c r="L5" s="96"/>
-      <c r="M5" s="96"/>
-      <c r="N5" s="96"/>
-      <c r="O5" s="96"/>
-      <c r="P5" s="96"/>
-      <c r="Q5" s="96"/>
-      <c r="R5" s="96"/>
-      <c r="S5" s="96"/>
-      <c r="T5" s="96"/>
-      <c r="U5" s="96"/>
-      <c r="V5" s="96"/>
-      <c r="W5" s="96"/>
-      <c r="X5" s="96"/>
-      <c r="Y5" s="96"/>
-      <c r="Z5" s="96"/>
-      <c r="AA5" s="96"/>
-      <c r="AB5" s="96"/>
-      <c r="AC5" s="96"/>
-      <c r="AD5" s="96"/>
-      <c r="AE5" s="96"/>
+      <c r="B5" s="102"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="102"/>
+      <c r="E5" s="102"/>
+      <c r="F5" s="102"/>
+      <c r="G5" s="102"/>
+      <c r="H5" s="102"/>
+      <c r="I5" s="102"/>
+      <c r="J5" s="102"/>
+      <c r="K5" s="102"/>
+      <c r="L5" s="102"/>
+      <c r="M5" s="102"/>
+      <c r="N5" s="102"/>
+      <c r="O5" s="102"/>
+      <c r="P5" s="102"/>
+      <c r="Q5" s="102"/>
+      <c r="R5" s="102"/>
+      <c r="S5" s="102"/>
+      <c r="T5" s="102"/>
+      <c r="U5" s="102"/>
+      <c r="V5" s="102"/>
+      <c r="W5" s="102"/>
+      <c r="X5" s="102"/>
+      <c r="Y5" s="102"/>
+      <c r="Z5" s="102"/>
+      <c r="AA5" s="102"/>
+      <c r="AB5" s="102"/>
+      <c r="AC5" s="102"/>
+      <c r="AD5" s="102"/>
+      <c r="AE5" s="102"/>
     </row>
     <row r="6" spans="1:31">
-      <c r="B6" s="96"/>
-      <c r="C6" s="96"/>
-      <c r="D6" s="96"/>
-      <c r="E6" s="96"/>
-      <c r="F6" s="96"/>
-      <c r="G6" s="96"/>
-      <c r="H6" s="96"/>
-      <c r="I6" s="96"/>
-      <c r="J6" s="96"/>
-      <c r="K6" s="96"/>
-      <c r="L6" s="96"/>
-      <c r="M6" s="96"/>
-      <c r="N6" s="96"/>
-      <c r="O6" s="96"/>
-      <c r="P6" s="96"/>
-      <c r="Q6" s="96"/>
-      <c r="R6" s="96"/>
-      <c r="S6" s="96"/>
-      <c r="T6" s="96"/>
-      <c r="U6" s="96"/>
-      <c r="V6" s="96"/>
-      <c r="W6" s="96"/>
-      <c r="X6" s="96"/>
-      <c r="Y6" s="96"/>
-      <c r="Z6" s="96"/>
-      <c r="AA6" s="96"/>
-      <c r="AB6" s="96"/>
-      <c r="AC6" s="96"/>
-      <c r="AD6" s="96"/>
-      <c r="AE6" s="96"/>
+      <c r="B6" s="102"/>
+      <c r="C6" s="102"/>
+      <c r="D6" s="102"/>
+      <c r="E6" s="102"/>
+      <c r="F6" s="102"/>
+      <c r="G6" s="102"/>
+      <c r="H6" s="102"/>
+      <c r="I6" s="102"/>
+      <c r="J6" s="102"/>
+      <c r="K6" s="102"/>
+      <c r="L6" s="102"/>
+      <c r="M6" s="102"/>
+      <c r="N6" s="102"/>
+      <c r="O6" s="102"/>
+      <c r="P6" s="102"/>
+      <c r="Q6" s="102"/>
+      <c r="R6" s="102"/>
+      <c r="S6" s="102"/>
+      <c r="T6" s="102"/>
+      <c r="U6" s="102"/>
+      <c r="V6" s="102"/>
+      <c r="W6" s="102"/>
+      <c r="X6" s="102"/>
+      <c r="Y6" s="102"/>
+      <c r="Z6" s="102"/>
+      <c r="AA6" s="102"/>
+      <c r="AB6" s="102"/>
+      <c r="AC6" s="102"/>
+      <c r="AD6" s="102"/>
+      <c r="AE6" s="102"/>
     </row>
     <row r="8" spans="1:31">
       <c r="B8" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31">
-      <c r="B10" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:R1"/>
     <mergeCell ref="B4:AE6"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="G2:J2"/>
     <mergeCell ref="K2:M2"/>
     <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:M1"/>
-    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P2:R2"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Summary!A1" display="Summary" xr:uid="{00000000-0004-0000-0900-000000000000}"/>
@@ -4613,202 +4849,206 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr defaultColWidth="5.28515625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.5703125" customWidth="1"/>
+    <col min="16" max="16" width="4.140625" customWidth="1"/>
+    <col min="17" max="17" width="5.28515625" customWidth="1"/>
+    <col min="18" max="18" width="3.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" thickBot="1">
+    <row r="1" spans="1:18" ht="15.75" thickBot="1">
       <c r="A1" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="117" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="99" t="s">
+        <v>217</v>
+      </c>
+      <c r="C1" s="100"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="125" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="126"/>
+      <c r="G1" s="99" t="s">
+        <v>218</v>
+      </c>
+      <c r="H1" s="100"/>
+      <c r="I1" s="100"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="86" t="s">
+        <v>210</v>
+      </c>
+      <c r="L1" s="127"/>
+      <c r="M1" s="87"/>
+      <c r="N1" s="99" t="s">
         <v>219</v>
       </c>
-      <c r="C1" s="118"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="120" t="s">
-        <v>22</v>
-      </c>
-      <c r="F1" s="121"/>
-      <c r="G1" s="117" t="s">
+      <c r="O1" s="101"/>
+      <c r="P1" s="85">
+        <v>45931</v>
+      </c>
+      <c r="Q1" s="85"/>
+      <c r="R1" s="85"/>
+    </row>
+    <row r="2" spans="1:18" ht="15.75" thickBot="1">
+      <c r="B2" s="99" t="s">
         <v>220</v>
       </c>
-      <c r="H1" s="118"/>
-      <c r="I1" s="118"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="115" t="s">
-        <v>212</v>
-      </c>
-      <c r="L1" s="122"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="117" t="s">
+      <c r="C2" s="100"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="128">
+        <v>0</v>
+      </c>
+      <c r="F2" s="129"/>
+      <c r="G2" s="99" t="s">
         <v>221</v>
       </c>
-      <c r="O1" s="119"/>
-      <c r="P1" s="115">
-        <v>45914</v>
-      </c>
-      <c r="Q1" s="116"/>
-    </row>
-    <row r="2" spans="1:17" ht="15.75" thickBot="1">
-      <c r="B2" s="117" t="s">
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="101"/>
+      <c r="K2" s="86" t="s">
+        <v>210</v>
+      </c>
+      <c r="L2" s="127"/>
+      <c r="M2" s="87"/>
+      <c r="N2" s="99" t="s">
         <v>222</v>
       </c>
-      <c r="C2" s="118"/>
-      <c r="D2" s="119"/>
-      <c r="E2" s="123">
-        <v>0</v>
-      </c>
-      <c r="F2" s="124"/>
-      <c r="G2" s="117" t="s">
-        <v>223</v>
-      </c>
-      <c r="H2" s="118"/>
-      <c r="I2" s="118"/>
-      <c r="J2" s="119"/>
-      <c r="K2" s="115" t="s">
-        <v>212</v>
-      </c>
-      <c r="L2" s="122"/>
-      <c r="M2" s="116"/>
-      <c r="N2" s="117" t="s">
-        <v>224</v>
-      </c>
-      <c r="O2" s="119"/>
-      <c r="P2" s="115">
-        <v>45914</v>
-      </c>
-      <c r="Q2" s="116"/>
-    </row>
-    <row r="5" spans="1:17" s="5" customFormat="1">
+      <c r="O2" s="101"/>
+      <c r="P2" s="85">
+        <v>45968</v>
+      </c>
+      <c r="Q2" s="85"/>
+      <c r="R2" s="85"/>
+    </row>
+    <row r="5" spans="1:18" s="5" customFormat="1">
       <c r="B5" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="D6" s="130" t="s">
+        <v>238</v>
+      </c>
+      <c r="O6" s="18" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
+      <c r="D7" s="18" t="s">
+        <v>239</v>
+      </c>
+      <c r="O7" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="O5" s="5" t="s">
+    </row>
+    <row r="8" spans="1:18">
+      <c r="D8" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="O8" s="18" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
-      <c r="D6" s="18" t="s">
+    <row r="9" spans="1:18">
+      <c r="D9" s="18" t="s">
         <v>241</v>
       </c>
-      <c r="O6" s="18" t="s">
+      <c r="O9" s="18" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
-      <c r="D7" s="18" t="s">
+    <row r="10" spans="1:18">
+      <c r="D10" s="18" t="s">
         <v>242</v>
       </c>
-      <c r="O7" s="18" t="s">
+      <c r="O10" s="18" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
-      <c r="D8" s="18" t="s">
-        <v>243</v>
-      </c>
-      <c r="O8" s="18" t="s">
+    <row r="11" spans="1:18">
+      <c r="O11" s="18"/>
+    </row>
+    <row r="13" spans="1:18">
+      <c r="B13" t="s">
+        <v>253</v>
+      </c>
+      <c r="D13" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="9" spans="1:17">
-      <c r="D9" s="18" t="s">
-        <v>244</v>
-      </c>
-      <c r="O9" s="18" t="s">
+      <c r="E13" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
+      <c r="D14" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="10" spans="1:17">
-      <c r="D10" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="O10" s="18" t="s">
+      <c r="E14" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
+      <c r="D15" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="11" spans="1:17">
-      <c r="O11" s="18"/>
-    </row>
-    <row r="13" spans="1:17">
-      <c r="B13" t="s">
-        <v>256</v>
-      </c>
-      <c r="D13" t="s">
-        <v>253</v>
-      </c>
-      <c r="E13" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17">
-      <c r="D14" t="s">
-        <v>254</v>
-      </c>
-      <c r="E14" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17">
-      <c r="D15" t="s">
-        <v>255</v>
-      </c>
       <c r="E15" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
       <c r="D16" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="E16" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="17" spans="4:5">
       <c r="D17" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E17" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="18" spans="4:5">
       <c r="D18" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E18" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="19" spans="4:5">
       <c r="D19" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="E19" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="P2:Q2"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="K1:M1"/>
     <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="G2:J2"/>
     <mergeCell ref="K2:M2"/>
     <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P1:R1"/>
+    <mergeCell ref="P2:R2"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Summary!A1" display="Summary" xr:uid="{00000000-0004-0000-0A00-000000000000}"/>
@@ -4818,388 +5058,140 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95590121-BC4B-4D68-B73E-610F888E8B68}">
-  <dimension ref="A1:Q37"/>
-  <sheetFormatPr defaultColWidth="4.42578125" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.5703125" customWidth="1"/>
-    <col min="17" max="17" width="7.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:17" ht="15.75" thickBot="1">
-      <c r="A1" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="117" t="s">
-        <v>219</v>
-      </c>
-      <c r="C1" s="118"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="120" t="s">
-        <v>289</v>
-      </c>
-      <c r="F1" s="121"/>
-      <c r="G1" s="117" t="s">
-        <v>220</v>
-      </c>
-      <c r="H1" s="118"/>
-      <c r="I1" s="118"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="115" t="s">
-        <v>212</v>
-      </c>
-      <c r="L1" s="122"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="117" t="s">
-        <v>221</v>
-      </c>
-      <c r="O1" s="119"/>
-      <c r="P1" s="115">
-        <v>45914</v>
-      </c>
-      <c r="Q1" s="116"/>
-    </row>
-    <row r="2" spans="1:17" ht="15.75" thickBot="1">
-      <c r="B2" s="117" t="s">
-        <v>222</v>
-      </c>
-      <c r="C2" s="118"/>
-      <c r="D2" s="119"/>
-      <c r="E2" s="123">
-        <v>0</v>
-      </c>
-      <c r="F2" s="124"/>
-      <c r="G2" s="117" t="s">
-        <v>223</v>
-      </c>
-      <c r="H2" s="118"/>
-      <c r="I2" s="118"/>
-      <c r="J2" s="119"/>
-      <c r="K2" s="115" t="s">
-        <v>212</v>
-      </c>
-      <c r="L2" s="122"/>
-      <c r="M2" s="116"/>
-      <c r="N2" s="117" t="s">
-        <v>224</v>
-      </c>
-      <c r="O2" s="119"/>
-      <c r="P2" s="115">
-        <v>45914</v>
-      </c>
-      <c r="Q2" s="116"/>
-    </row>
-    <row r="4" spans="1:17">
-      <c r="C4" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="18">
-      <c r="C6" s="134" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17">
-      <c r="C7" s="18" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17">
-      <c r="C8" s="18" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17">
-      <c r="C9" s="18" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17">
-      <c r="C10" s="18" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17">
-      <c r="C11" s="18" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17">
-      <c r="C12" s="18" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="18">
-      <c r="C14" s="134" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17">
-      <c r="C15" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17">
-      <c r="C16" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="17" spans="3:3">
-      <c r="C17" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="18" spans="3:3">
-      <c r="C18" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="19" spans="3:3">
-      <c r="C19" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="21" spans="3:3" ht="18">
-      <c r="C21" s="134" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="22" spans="3:3">
-      <c r="C22" s="18" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="23" spans="3:3">
-      <c r="C23" s="18" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="24" spans="3:3">
-      <c r="C24" s="18" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="25" spans="3:3">
-      <c r="C25" s="18" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="27" spans="3:3" ht="18">
-      <c r="C27" s="134" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="28" spans="3:3">
-      <c r="C28" s="18" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="29" spans="3:3">
-      <c r="C29" s="18" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="30" spans="3:3">
-      <c r="C30" s="18" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="31" spans="3:3">
-      <c r="C31" s="18" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="33" spans="3:3" ht="18">
-      <c r="C33" s="134" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="34" spans="3:3">
-      <c r="C34" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="35" spans="3:3">
-      <c r="C35" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="36" spans="3:3">
-      <c r="C36" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="37" spans="3:3">
-      <c r="C37" t="s">
-        <v>312</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:M1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="A1" location="Summary!A1" display="Summary" xr:uid="{787EF59B-4D9C-40F3-9D46-32BA474BC12D}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:CD48"/>
+  <dimension ref="A1:BX48"/>
   <sheetFormatPr defaultColWidth="4.7109375" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:82" s="2" customFormat="1">
-      <c r="A1" s="79" t="s">
+    <row r="1" spans="1:76" s="136" customFormat="1">
+      <c r="A1" s="131" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="79" t="s">
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="131" t="s">
+        <v>323</v>
+      </c>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
+      <c r="H1" s="132"/>
+      <c r="I1" s="132"/>
+      <c r="J1" s="132"/>
+      <c r="K1" s="132"/>
+      <c r="L1" s="132"/>
+      <c r="M1" s="132"/>
+      <c r="N1" s="132"/>
+      <c r="O1" s="132"/>
+      <c r="P1" s="132"/>
+      <c r="Q1" s="132"/>
+      <c r="R1" s="133"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="80"/>
-      <c r="M1" s="80"/>
-      <c r="N1" s="80"/>
-      <c r="O1" s="80"/>
-      <c r="P1" s="80"/>
-      <c r="Q1" s="81"/>
-      <c r="R1" s="82"/>
-      <c r="S1" s="83"/>
-      <c r="T1" s="83"/>
-      <c r="U1" s="83"/>
-      <c r="V1" s="83"/>
-      <c r="W1" s="83"/>
-      <c r="X1" s="83"/>
-      <c r="Y1" s="70"/>
-      <c r="Z1" s="70"/>
-      <c r="AA1" s="70" t="s">
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134" t="s">
         <v>2</v>
       </c>
-      <c r="AB1" s="70"/>
-      <c r="AC1" s="70"/>
-      <c r="AD1" s="70" t="s">
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="135"/>
+      <c r="AB1" s="135"/>
+      <c r="AC1" s="135"/>
+      <c r="AD1" s="135"/>
+      <c r="AE1" s="135"/>
+      <c r="AF1" s="135"/>
+      <c r="AG1" s="135"/>
+      <c r="AH1" s="135"/>
+      <c r="AI1" s="135"/>
+      <c r="AJ1" s="135"/>
+      <c r="AK1" s="135"/>
+      <c r="AL1" s="135"/>
+      <c r="AM1" s="135"/>
+      <c r="AN1" s="135"/>
+      <c r="AO1" s="135"/>
+      <c r="AP1" s="135"/>
+      <c r="AQ1" s="135"/>
+      <c r="AR1" s="135"/>
+      <c r="AS1" s="135"/>
+      <c r="AT1" s="135"/>
+      <c r="AU1" s="135"/>
+      <c r="AV1" s="135"/>
+      <c r="AW1" s="135"/>
+      <c r="AX1" s="135"/>
+      <c r="AY1" s="135"/>
+      <c r="AZ1" s="135"/>
+      <c r="BA1" s="135"/>
+      <c r="BB1" s="135"/>
+      <c r="BC1" s="135"/>
+      <c r="BD1" s="135"/>
+      <c r="BE1" s="135"/>
+      <c r="BF1" s="135"/>
+      <c r="BG1" s="135"/>
+      <c r="BH1" s="135"/>
+      <c r="BI1" s="135"/>
+      <c r="BJ1" s="135"/>
+      <c r="BK1" s="135"/>
+      <c r="BL1" s="135"/>
+      <c r="BM1" s="135"/>
+      <c r="BN1" s="135"/>
+      <c r="BO1" s="135"/>
+      <c r="BP1" s="135"/>
+      <c r="BQ1" s="135"/>
+      <c r="BR1" s="135"/>
+      <c r="BS1" s="135"/>
+      <c r="BT1" s="135"/>
+      <c r="BU1" s="135"/>
+      <c r="BV1" s="135"/>
+      <c r="BW1" s="135"/>
+      <c r="BX1" s="135"/>
+    </row>
+    <row r="2" spans="1:76" s="2" customFormat="1">
+      <c r="A2" s="77" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="77" t="s">
+        <v>322</v>
+      </c>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="78"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="79"/>
+      <c r="S2" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="AE1" s="70"/>
-      <c r="AF1" s="70"/>
-      <c r="AG1" s="1"/>
-      <c r="AH1" s="1"/>
-      <c r="AI1" s="1"/>
-      <c r="AJ1" s="1"/>
-      <c r="AK1" s="1"/>
-      <c r="AL1" s="1"/>
-      <c r="AM1" s="1"/>
-      <c r="AN1" s="1"/>
-      <c r="AO1" s="1"/>
-      <c r="AP1" s="1"/>
-      <c r="AQ1" s="1"/>
-      <c r="AR1" s="1"/>
-      <c r="AS1" s="1"/>
-      <c r="AT1" s="1"/>
-      <c r="AU1" s="1"/>
-      <c r="AV1" s="1"/>
-      <c r="AW1" s="1"/>
-      <c r="AX1" s="1"/>
-      <c r="AY1" s="1"/>
-      <c r="AZ1" s="1"/>
-      <c r="BA1" s="1"/>
-      <c r="BB1" s="1"/>
-      <c r="BC1" s="1"/>
-      <c r="BD1" s="1"/>
-      <c r="BE1" s="1"/>
-      <c r="BF1" s="1"/>
-      <c r="BG1" s="1"/>
-      <c r="BH1" s="1"/>
-      <c r="BI1" s="1"/>
-      <c r="BJ1" s="1"/>
-      <c r="BK1" s="1"/>
-      <c r="BL1" s="1"/>
-      <c r="BM1" s="1"/>
-      <c r="BN1" s="1"/>
-      <c r="BO1" s="1"/>
-      <c r="BP1" s="1"/>
-      <c r="BQ1" s="1"/>
-      <c r="BR1" s="1"/>
-      <c r="BS1" s="1"/>
-      <c r="BT1" s="1"/>
-      <c r="BU1" s="1"/>
-      <c r="BV1" s="1"/>
-      <c r="BW1" s="1"/>
-      <c r="BX1" s="1"/>
-      <c r="BY1" s="1"/>
-      <c r="BZ1" s="1"/>
-      <c r="CA1" s="1"/>
-      <c r="CB1" s="1"/>
-      <c r="CC1" s="1"/>
-      <c r="CD1" s="1"/>
-    </row>
-    <row r="2" spans="1:82" s="2" customFormat="1">
-      <c r="A2" s="72" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="74"/>
-      <c r="K2" s="72" t="s">
-        <v>7</v>
-      </c>
-      <c r="L2" s="73"/>
-      <c r="M2" s="73"/>
-      <c r="N2" s="73"/>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="74"/>
-      <c r="R2" s="72" t="s">
-        <v>6</v>
-      </c>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
-      <c r="W2" s="73"/>
-      <c r="X2" s="73"/>
-      <c r="Y2" s="70" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z2" s="70"/>
-      <c r="AA2" s="70" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB2" s="70"/>
-      <c r="AC2" s="70"/>
-      <c r="AD2" s="125">
-        <v>45914</v>
-      </c>
-      <c r="AE2" s="125"/>
-      <c r="AF2" s="125"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76" t="s">
+        <v>254</v>
+      </c>
+      <c r="V2" s="76"/>
+      <c r="W2" s="76"/>
+      <c r="X2" s="85">
+        <v>45931</v>
+      </c>
+      <c r="Y2" s="85"/>
+      <c r="Z2" s="85"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
       <c r="AG2" s="1"/>
       <c r="AH2" s="1"/>
       <c r="AI2" s="1"/>
@@ -5244,52 +5236,46 @@
       <c r="BV2" s="1"/>
       <c r="BW2" s="1"/>
       <c r="BX2" s="1"/>
-      <c r="BY2" s="1"/>
-      <c r="BZ2" s="1"/>
-      <c r="CA2" s="1"/>
-      <c r="CB2" s="1"/>
-      <c r="CC2" s="1"/>
-      <c r="CD2" s="1"/>
-    </row>
-    <row r="3" spans="1:82" s="2" customFormat="1">
-      <c r="A3" s="75"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="77"/>
-      <c r="K3" s="75"/>
-      <c r="L3" s="76"/>
-      <c r="M3" s="76"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="75"/>
-      <c r="S3" s="76"/>
+    </row>
+    <row r="3" spans="1:76" s="2" customFormat="1">
+      <c r="A3" s="80"/>
+      <c r="B3" s="81"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="81"/>
+      <c r="K3" s="81"/>
+      <c r="L3" s="81"/>
+      <c r="M3" s="81"/>
+      <c r="N3" s="81"/>
+      <c r="O3" s="81"/>
+      <c r="P3" s="81"/>
+      <c r="Q3" s="81"/>
+      <c r="R3" s="82"/>
+      <c r="S3" s="76" t="s">
+        <v>4</v>
+      </c>
       <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
+      <c r="U3" s="76" t="s">
+        <v>254</v>
+      </c>
       <c r="V3" s="76"/>
       <c r="W3" s="76"/>
-      <c r="X3" s="76"/>
-      <c r="Y3" s="70" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z3" s="70"/>
-      <c r="AA3" s="70" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB3" s="70"/>
-      <c r="AC3" s="70"/>
-      <c r="AD3" s="125">
-        <v>45914</v>
-      </c>
-      <c r="AE3" s="125"/>
-      <c r="AF3" s="125"/>
+      <c r="X3" s="85">
+        <v>45968</v>
+      </c>
+      <c r="Y3" s="85"/>
+      <c r="Z3" s="85"/>
+      <c r="AA3" s="1"/>
+      <c r="AB3" s="1"/>
+      <c r="AC3" s="1"/>
+      <c r="AD3" s="1"/>
+      <c r="AE3" s="1"/>
+      <c r="AF3" s="1"/>
       <c r="AG3" s="1"/>
       <c r="AH3" s="1"/>
       <c r="AI3" s="1"/>
@@ -5334,735 +5320,727 @@
       <c r="BV3" s="1"/>
       <c r="BW3" s="1"/>
       <c r="BX3" s="1"/>
-      <c r="BY3" s="1"/>
-      <c r="BZ3" s="1"/>
-      <c r="CA3" s="1"/>
-      <c r="CB3" s="1"/>
-      <c r="CC3" s="1"/>
-      <c r="CD3" s="1"/>
-    </row>
-    <row r="7" spans="1:82">
-      <c r="B7" s="78" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="78"/>
-      <c r="D7" s="78" t="s">
+    </row>
+    <row r="7" spans="1:76">
+      <c r="B7" s="84" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="84"/>
+      <c r="D7" s="84" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="84"/>
+      <c r="F7" s="84"/>
+      <c r="G7" s="84"/>
+      <c r="H7" s="84"/>
+      <c r="I7" s="84"/>
+      <c r="J7" s="84"/>
+      <c r="K7" s="84"/>
+      <c r="L7" s="84"/>
+      <c r="M7" s="84"/>
+      <c r="N7" s="84"/>
+      <c r="O7" s="84"/>
+      <c r="P7" s="84"/>
+      <c r="Q7" s="84"/>
+      <c r="R7" s="84"/>
+      <c r="S7" s="84"/>
+    </row>
+    <row r="8" spans="1:76">
+      <c r="B8" s="76">
+        <v>1</v>
+      </c>
+      <c r="C8" s="76"/>
+      <c r="D8" s="83" t="s">
+        <v>324</v>
+      </c>
+      <c r="E8" s="83"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="83"/>
+      <c r="I8" s="83"/>
+      <c r="J8" s="83"/>
+      <c r="K8" s="83"/>
+      <c r="L8" s="83"/>
+      <c r="M8" s="83"/>
+      <c r="N8" s="83"/>
+      <c r="O8" s="83"/>
+      <c r="P8" s="83"/>
+      <c r="Q8" s="83"/>
+      <c r="R8" s="83"/>
+      <c r="S8" s="83"/>
+    </row>
+    <row r="9" spans="1:76">
+      <c r="B9" s="76">
+        <v>2</v>
+      </c>
+      <c r="C9" s="76"/>
+      <c r="D9" s="83" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="83"/>
+      <c r="I9" s="83"/>
+      <c r="J9" s="83"/>
+      <c r="K9" s="83"/>
+      <c r="L9" s="83"/>
+      <c r="M9" s="83"/>
+      <c r="N9" s="83"/>
+      <c r="O9" s="83"/>
+      <c r="P9" s="83"/>
+      <c r="Q9" s="83"/>
+      <c r="R9" s="83"/>
+      <c r="S9" s="83"/>
+    </row>
+    <row r="10" spans="1:76">
+      <c r="B10" s="76">
+        <v>3</v>
+      </c>
+      <c r="C10" s="76"/>
+      <c r="D10" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="78"/>
-      <c r="F7" s="78"/>
-      <c r="G7" s="78"/>
-      <c r="H7" s="78"/>
-      <c r="I7" s="78"/>
-      <c r="J7" s="78"/>
-      <c r="K7" s="78"/>
-      <c r="L7" s="78"/>
-      <c r="M7" s="78"/>
-      <c r="N7" s="78"/>
-      <c r="O7" s="78"/>
-      <c r="P7" s="78"/>
-      <c r="Q7" s="78"/>
-      <c r="R7" s="78"/>
-      <c r="S7" s="78"/>
-    </row>
-    <row r="8" spans="1:82">
-      <c r="B8" s="70">
-        <v>1</v>
-      </c>
-      <c r="C8" s="70"/>
-      <c r="D8" s="71" t="s">
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="61"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="61"/>
+      <c r="K10" s="61"/>
+      <c r="L10" s="61"/>
+      <c r="M10" s="61"/>
+      <c r="N10" s="61"/>
+      <c r="O10" s="61"/>
+      <c r="P10" s="61"/>
+      <c r="Q10" s="61"/>
+      <c r="R10" s="61"/>
+      <c r="S10" s="62"/>
+    </row>
+    <row r="11" spans="1:76">
+      <c r="B11" s="76">
+        <v>4</v>
+      </c>
+      <c r="C11" s="76"/>
+      <c r="D11" s="60" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="61"/>
+      <c r="F11" s="61"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="61"/>
+      <c r="K11" s="61"/>
+      <c r="L11" s="61"/>
+      <c r="M11" s="61"/>
+      <c r="N11" s="61"/>
+      <c r="O11" s="61"/>
+      <c r="P11" s="61"/>
+      <c r="Q11" s="61"/>
+      <c r="R11" s="61"/>
+      <c r="S11" s="62"/>
+    </row>
+    <row r="12" spans="1:76">
+      <c r="B12" s="76">
+        <v>5</v>
+      </c>
+      <c r="C12" s="76"/>
+      <c r="D12" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="71"/>
-      <c r="F8" s="71"/>
-      <c r="G8" s="71"/>
-      <c r="H8" s="71"/>
-      <c r="I8" s="71"/>
-      <c r="J8" s="71"/>
-      <c r="K8" s="71"/>
-      <c r="L8" s="71"/>
-      <c r="M8" s="71"/>
-      <c r="N8" s="71"/>
-      <c r="O8" s="71"/>
-      <c r="P8" s="71"/>
-      <c r="Q8" s="71"/>
-      <c r="R8" s="71"/>
-      <c r="S8" s="71"/>
-    </row>
-    <row r="9" spans="1:82">
-      <c r="B9" s="70">
-        <v>2</v>
-      </c>
-      <c r="C9" s="70"/>
-      <c r="D9" s="71" t="s">
+      <c r="E12" s="61"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61"/>
+      <c r="I12" s="61"/>
+      <c r="J12" s="61"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="61"/>
+      <c r="M12" s="61"/>
+      <c r="N12" s="61"/>
+      <c r="O12" s="61"/>
+      <c r="P12" s="61"/>
+      <c r="Q12" s="61"/>
+      <c r="R12" s="61"/>
+      <c r="S12" s="62"/>
+    </row>
+    <row r="13" spans="1:76">
+      <c r="B13" s="76">
+        <v>6</v>
+      </c>
+      <c r="C13" s="76"/>
+      <c r="D13" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="71"/>
-      <c r="F9" s="71"/>
-      <c r="G9" s="71"/>
-      <c r="H9" s="71"/>
-      <c r="I9" s="71"/>
-      <c r="J9" s="71"/>
-      <c r="K9" s="71"/>
-      <c r="L9" s="71"/>
-      <c r="M9" s="71"/>
-      <c r="N9" s="71"/>
-      <c r="O9" s="71"/>
-      <c r="P9" s="71"/>
-      <c r="Q9" s="71"/>
-      <c r="R9" s="71"/>
-      <c r="S9" s="71"/>
-    </row>
-    <row r="10" spans="1:82">
-      <c r="B10" s="70">
-        <v>3</v>
-      </c>
-      <c r="C10" s="70"/>
-      <c r="D10" s="71" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" s="71"/>
-      <c r="F10" s="71"/>
-      <c r="G10" s="71"/>
-      <c r="H10" s="71"/>
-      <c r="I10" s="71"/>
-      <c r="J10" s="71"/>
-      <c r="K10" s="71"/>
-      <c r="L10" s="71"/>
-      <c r="M10" s="71"/>
-      <c r="N10" s="71"/>
-      <c r="O10" s="71"/>
-      <c r="P10" s="71"/>
-      <c r="Q10" s="71"/>
-      <c r="R10" s="71"/>
-      <c r="S10" s="71"/>
-    </row>
-    <row r="11" spans="1:82">
-      <c r="B11" s="70">
-        <v>4</v>
-      </c>
-      <c r="C11" s="70"/>
-      <c r="D11" s="71" t="s">
+      <c r="E13" s="61"/>
+      <c r="F13" s="61"/>
+      <c r="G13" s="61"/>
+      <c r="H13" s="61"/>
+      <c r="I13" s="61"/>
+      <c r="J13" s="61"/>
+      <c r="K13" s="61"/>
+      <c r="L13" s="61"/>
+      <c r="M13" s="61"/>
+      <c r="N13" s="61"/>
+      <c r="O13" s="61"/>
+      <c r="P13" s="61"/>
+      <c r="Q13" s="61"/>
+      <c r="R13" s="61"/>
+      <c r="S13" s="62"/>
+    </row>
+    <row r="14" spans="1:76">
+      <c r="B14" s="76">
+        <v>7</v>
+      </c>
+      <c r="C14" s="76"/>
+      <c r="D14" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="71"/>
-      <c r="F11" s="71"/>
-      <c r="G11" s="71"/>
-      <c r="H11" s="71"/>
-      <c r="I11" s="71"/>
-      <c r="J11" s="71"/>
-      <c r="K11" s="71"/>
-      <c r="L11" s="71"/>
-      <c r="M11" s="71"/>
-      <c r="N11" s="71"/>
-      <c r="O11" s="71"/>
-      <c r="P11" s="71"/>
-      <c r="Q11" s="71"/>
-      <c r="R11" s="71"/>
-      <c r="S11" s="71"/>
-    </row>
-    <row r="12" spans="1:82">
-      <c r="B12" s="70">
-        <v>5</v>
-      </c>
-      <c r="C12" s="70"/>
-      <c r="D12" s="71" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="71"/>
-      <c r="F12" s="71"/>
-      <c r="G12" s="71"/>
-      <c r="H12" s="71"/>
-      <c r="I12" s="71"/>
-      <c r="J12" s="71"/>
-      <c r="K12" s="71"/>
-      <c r="L12" s="71"/>
-      <c r="M12" s="71"/>
-      <c r="N12" s="71"/>
-      <c r="O12" s="71"/>
-      <c r="P12" s="71"/>
-      <c r="Q12" s="71"/>
-      <c r="R12" s="71"/>
-      <c r="S12" s="71"/>
-    </row>
-    <row r="13" spans="1:82">
-      <c r="B13" s="70">
-        <v>6</v>
-      </c>
-      <c r="C13" s="70"/>
-      <c r="D13" s="71" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="71"/>
-      <c r="F13" s="71"/>
-      <c r="G13" s="71"/>
-      <c r="H13" s="71"/>
-      <c r="I13" s="71"/>
-      <c r="J13" s="71"/>
-      <c r="K13" s="71"/>
-      <c r="L13" s="71"/>
-      <c r="M13" s="71"/>
-      <c r="N13" s="71"/>
-      <c r="O13" s="71"/>
-      <c r="P13" s="71"/>
-      <c r="Q13" s="71"/>
-      <c r="R13" s="71"/>
-      <c r="S13" s="71"/>
-    </row>
-    <row r="14" spans="1:82">
-      <c r="B14" s="70">
-        <v>7</v>
-      </c>
-      <c r="C14" s="70"/>
-      <c r="D14" s="71" t="s">
-        <v>236</v>
-      </c>
-      <c r="E14" s="71"/>
-      <c r="F14" s="71"/>
-      <c r="G14" s="71"/>
-      <c r="H14" s="71"/>
-      <c r="I14" s="71"/>
-      <c r="J14" s="71"/>
-      <c r="K14" s="71"/>
-      <c r="L14" s="71"/>
-      <c r="M14" s="71"/>
-      <c r="N14" s="71"/>
-      <c r="O14" s="71"/>
-      <c r="P14" s="71"/>
-      <c r="Q14" s="71"/>
-      <c r="R14" s="71"/>
-      <c r="S14" s="71"/>
-    </row>
-    <row r="15" spans="1:82">
-      <c r="B15" s="70">
+      <c r="E14" s="61"/>
+      <c r="F14" s="61"/>
+      <c r="G14" s="61"/>
+      <c r="H14" s="61"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="61"/>
+      <c r="K14" s="61"/>
+      <c r="L14" s="61"/>
+      <c r="M14" s="61"/>
+      <c r="N14" s="61"/>
+      <c r="O14" s="61"/>
+      <c r="P14" s="61"/>
+      <c r="Q14" s="61"/>
+      <c r="R14" s="61"/>
+      <c r="S14" s="62"/>
+    </row>
+    <row r="15" spans="1:76">
+      <c r="B15" s="76">
         <v>8</v>
       </c>
-      <c r="C15" s="70"/>
-      <c r="D15" s="71" t="s">
-        <v>237</v>
-      </c>
-      <c r="E15" s="71"/>
-      <c r="F15" s="71"/>
-      <c r="G15" s="71"/>
-      <c r="H15" s="71"/>
-      <c r="I15" s="71"/>
-      <c r="J15" s="71"/>
-      <c r="K15" s="71"/>
-      <c r="L15" s="71"/>
-      <c r="M15" s="71"/>
-      <c r="N15" s="71"/>
-      <c r="O15" s="71"/>
-      <c r="P15" s="71"/>
-      <c r="Q15" s="71"/>
-      <c r="R15" s="71"/>
-      <c r="S15" s="71"/>
-    </row>
-    <row r="16" spans="1:82">
-      <c r="B16" s="70">
+      <c r="C15" s="76"/>
+      <c r="D15" s="60" t="s">
+        <v>234</v>
+      </c>
+      <c r="E15" s="61"/>
+      <c r="F15" s="61"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="61"/>
+      <c r="I15" s="61"/>
+      <c r="J15" s="61"/>
+      <c r="K15" s="61"/>
+      <c r="L15" s="61"/>
+      <c r="M15" s="61"/>
+      <c r="N15" s="61"/>
+      <c r="O15" s="61"/>
+      <c r="P15" s="61"/>
+      <c r="Q15" s="61"/>
+      <c r="R15" s="61"/>
+      <c r="S15" s="62"/>
+    </row>
+    <row r="16" spans="1:76">
+      <c r="B16" s="76">
         <v>9</v>
       </c>
-      <c r="C16" s="70"/>
-      <c r="D16" s="71" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" s="71"/>
-      <c r="F16" s="71"/>
-      <c r="G16" s="71"/>
-      <c r="H16" s="71"/>
-      <c r="I16" s="71"/>
-      <c r="J16" s="71"/>
-      <c r="K16" s="71"/>
-      <c r="L16" s="71"/>
-      <c r="M16" s="71"/>
-      <c r="N16" s="71"/>
-      <c r="O16" s="71"/>
-      <c r="P16" s="71"/>
-      <c r="Q16" s="71"/>
-      <c r="R16" s="71"/>
-      <c r="S16" s="71"/>
+      <c r="C16" s="76"/>
+      <c r="D16" s="60" t="s">
+        <v>235</v>
+      </c>
+      <c r="E16" s="61"/>
+      <c r="F16" s="61"/>
+      <c r="G16" s="61"/>
+      <c r="H16" s="61"/>
+      <c r="I16" s="61"/>
+      <c r="J16" s="61"/>
+      <c r="K16" s="61"/>
+      <c r="L16" s="61"/>
+      <c r="M16" s="61"/>
+      <c r="N16" s="61"/>
+      <c r="O16" s="61"/>
+      <c r="P16" s="61"/>
+      <c r="Q16" s="61"/>
+      <c r="R16" s="61"/>
+      <c r="S16" s="62"/>
     </row>
     <row r="17" spans="2:19">
-      <c r="B17" s="70">
+      <c r="B17" s="76">
         <v>10</v>
       </c>
-      <c r="C17" s="70"/>
-      <c r="D17" s="71" t="s">
-        <v>314</v>
-      </c>
-      <c r="E17" s="71"/>
-      <c r="F17" s="71"/>
-      <c r="G17" s="71"/>
-      <c r="H17" s="71"/>
-      <c r="I17" s="71"/>
-      <c r="J17" s="71"/>
-      <c r="K17" s="71"/>
-      <c r="L17" s="71"/>
-      <c r="M17" s="71"/>
-      <c r="N17" s="71"/>
-      <c r="O17" s="71"/>
-      <c r="P17" s="71"/>
-      <c r="Q17" s="71"/>
-      <c r="R17" s="71"/>
-      <c r="S17" s="71"/>
+      <c r="C17" s="76"/>
+      <c r="D17" s="60" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="61"/>
+      <c r="F17" s="61"/>
+      <c r="G17" s="61"/>
+      <c r="H17" s="61"/>
+      <c r="I17" s="61"/>
+      <c r="J17" s="61"/>
+      <c r="K17" s="61"/>
+      <c r="L17" s="61"/>
+      <c r="M17" s="61"/>
+      <c r="N17" s="61"/>
+      <c r="O17" s="61"/>
+      <c r="P17" s="61"/>
+      <c r="Q17" s="61"/>
+      <c r="R17" s="61"/>
+      <c r="S17" s="62"/>
     </row>
     <row r="18" spans="2:19">
-      <c r="B18" s="70"/>
-      <c r="C18" s="70"/>
-      <c r="D18" s="71"/>
-      <c r="E18" s="71"/>
-      <c r="F18" s="71"/>
-      <c r="G18" s="71"/>
-      <c r="H18" s="71"/>
-      <c r="I18" s="71"/>
-      <c r="J18" s="71"/>
-      <c r="K18" s="71"/>
-      <c r="L18" s="71"/>
-      <c r="M18" s="71"/>
-      <c r="N18" s="71"/>
-      <c r="O18" s="71"/>
-      <c r="P18" s="71"/>
-      <c r="Q18" s="71"/>
-      <c r="R18" s="71"/>
-      <c r="S18" s="71"/>
+      <c r="B18" s="76"/>
+      <c r="C18" s="76"/>
+      <c r="D18" s="83"/>
+      <c r="E18" s="83"/>
+      <c r="F18" s="83"/>
+      <c r="G18" s="83"/>
+      <c r="H18" s="83"/>
+      <c r="I18" s="83"/>
+      <c r="J18" s="83"/>
+      <c r="K18" s="83"/>
+      <c r="L18" s="83"/>
+      <c r="M18" s="83"/>
+      <c r="N18" s="83"/>
+      <c r="O18" s="83"/>
+      <c r="P18" s="83"/>
+      <c r="Q18" s="83"/>
+      <c r="R18" s="83"/>
+      <c r="S18" s="83"/>
     </row>
     <row r="19" spans="2:19">
-      <c r="B19" s="70"/>
-      <c r="C19" s="70"/>
-      <c r="D19" s="71"/>
-      <c r="E19" s="71"/>
-      <c r="F19" s="71"/>
-      <c r="G19" s="71"/>
-      <c r="H19" s="71"/>
-      <c r="I19" s="71"/>
-      <c r="J19" s="71"/>
-      <c r="K19" s="71"/>
-      <c r="L19" s="71"/>
-      <c r="M19" s="71"/>
-      <c r="N19" s="71"/>
-      <c r="O19" s="71"/>
-      <c r="P19" s="71"/>
-      <c r="Q19" s="71"/>
-      <c r="R19" s="71"/>
-      <c r="S19" s="71"/>
+      <c r="B19" s="76"/>
+      <c r="C19" s="76"/>
+      <c r="D19" s="83"/>
+      <c r="E19" s="83"/>
+      <c r="F19" s="83"/>
+      <c r="G19" s="83"/>
+      <c r="H19" s="83"/>
+      <c r="I19" s="83"/>
+      <c r="J19" s="83"/>
+      <c r="K19" s="83"/>
+      <c r="L19" s="83"/>
+      <c r="M19" s="83"/>
+      <c r="N19" s="83"/>
+      <c r="O19" s="83"/>
+      <c r="P19" s="83"/>
+      <c r="Q19" s="83"/>
+      <c r="R19" s="83"/>
+      <c r="S19" s="83"/>
     </row>
     <row r="20" spans="2:19">
-      <c r="B20" s="70"/>
-      <c r="C20" s="70"/>
-      <c r="D20" s="71"/>
-      <c r="E20" s="71"/>
-      <c r="F20" s="71"/>
-      <c r="G20" s="71"/>
-      <c r="H20" s="71"/>
-      <c r="I20" s="71"/>
-      <c r="J20" s="71"/>
-      <c r="K20" s="71"/>
-      <c r="L20" s="71"/>
-      <c r="M20" s="71"/>
-      <c r="N20" s="71"/>
-      <c r="O20" s="71"/>
-      <c r="P20" s="71"/>
-      <c r="Q20" s="71"/>
-      <c r="R20" s="71"/>
-      <c r="S20" s="71"/>
+      <c r="B20" s="76"/>
+      <c r="C20" s="76"/>
+      <c r="D20" s="83"/>
+      <c r="E20" s="83"/>
+      <c r="F20" s="83"/>
+      <c r="G20" s="83"/>
+      <c r="H20" s="83"/>
+      <c r="I20" s="83"/>
+      <c r="J20" s="83"/>
+      <c r="K20" s="83"/>
+      <c r="L20" s="83"/>
+      <c r="M20" s="83"/>
+      <c r="N20" s="83"/>
+      <c r="O20" s="83"/>
+      <c r="P20" s="83"/>
+      <c r="Q20" s="83"/>
+      <c r="R20" s="83"/>
+      <c r="S20" s="83"/>
     </row>
     <row r="21" spans="2:19">
-      <c r="B21" s="70"/>
-      <c r="C21" s="70"/>
-      <c r="D21" s="71"/>
-      <c r="E21" s="71"/>
-      <c r="F21" s="71"/>
-      <c r="G21" s="71"/>
-      <c r="H21" s="71"/>
-      <c r="I21" s="71"/>
-      <c r="J21" s="71"/>
-      <c r="K21" s="71"/>
-      <c r="L21" s="71"/>
-      <c r="M21" s="71"/>
-      <c r="N21" s="71"/>
-      <c r="O21" s="71"/>
-      <c r="P21" s="71"/>
-      <c r="Q21" s="71"/>
-      <c r="R21" s="71"/>
-      <c r="S21" s="71"/>
+      <c r="B21" s="76"/>
+      <c r="C21" s="76"/>
+      <c r="D21" s="83"/>
+      <c r="E21" s="83"/>
+      <c r="F21" s="83"/>
+      <c r="G21" s="83"/>
+      <c r="H21" s="83"/>
+      <c r="I21" s="83"/>
+      <c r="J21" s="83"/>
+      <c r="K21" s="83"/>
+      <c r="L21" s="83"/>
+      <c r="M21" s="83"/>
+      <c r="N21" s="83"/>
+      <c r="O21" s="83"/>
+      <c r="P21" s="83"/>
+      <c r="Q21" s="83"/>
+      <c r="R21" s="83"/>
+      <c r="S21" s="83"/>
     </row>
     <row r="22" spans="2:19">
-      <c r="B22" s="70"/>
-      <c r="C22" s="70"/>
-      <c r="D22" s="71"/>
-      <c r="E22" s="71"/>
-      <c r="F22" s="71"/>
-      <c r="G22" s="71"/>
-      <c r="H22" s="71"/>
-      <c r="I22" s="71"/>
-      <c r="J22" s="71"/>
-      <c r="K22" s="71"/>
-      <c r="L22" s="71"/>
-      <c r="M22" s="71"/>
-      <c r="N22" s="71"/>
-      <c r="O22" s="71"/>
-      <c r="P22" s="71"/>
-      <c r="Q22" s="71"/>
-      <c r="R22" s="71"/>
-      <c r="S22" s="71"/>
-    </row>
-    <row r="36" spans="3:25" s="131" customFormat="1"/>
+      <c r="B22" s="76"/>
+      <c r="C22" s="76"/>
+      <c r="D22" s="83"/>
+      <c r="E22" s="83"/>
+      <c r="F22" s="83"/>
+      <c r="G22" s="83"/>
+      <c r="H22" s="83"/>
+      <c r="I22" s="83"/>
+      <c r="J22" s="83"/>
+      <c r="K22" s="83"/>
+      <c r="L22" s="83"/>
+      <c r="M22" s="83"/>
+      <c r="N22" s="83"/>
+      <c r="O22" s="83"/>
+      <c r="P22" s="83"/>
+      <c r="Q22" s="83"/>
+      <c r="R22" s="83"/>
+      <c r="S22" s="83"/>
+    </row>
+    <row r="36" spans="3:25" s="56" customFormat="1"/>
     <row r="37" spans="3:25">
       <c r="C37" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="38" spans="3:25">
+      <c r="C38" s="74" t="s">
+        <v>263</v>
+      </c>
+      <c r="D38" s="74"/>
+      <c r="E38" s="74"/>
+      <c r="F38" s="74"/>
+      <c r="G38" s="74"/>
+      <c r="H38" s="74"/>
+      <c r="I38" s="74"/>
+      <c r="J38" s="74"/>
+      <c r="K38" s="74"/>
+      <c r="L38" s="74"/>
+      <c r="M38" s="74"/>
+      <c r="N38" s="74"/>
+      <c r="O38" s="74" t="s">
+        <v>264</v>
+      </c>
+      <c r="P38" s="74"/>
+      <c r="Q38" s="74"/>
+      <c r="R38" s="74"/>
+      <c r="S38" s="74"/>
+      <c r="T38" s="74"/>
+      <c r="U38" s="74"/>
+      <c r="V38" s="74"/>
+      <c r="W38" s="74"/>
+      <c r="X38" s="74"/>
+      <c r="Y38" s="74"/>
+    </row>
+    <row r="39" spans="3:25" ht="68.099999999999994" customHeight="1">
+      <c r="C39" s="74" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="38" spans="3:25">
-      <c r="C38" s="132" t="s">
+      <c r="D39" s="74"/>
+      <c r="E39" s="74"/>
+      <c r="F39" s="74"/>
+      <c r="G39" s="74"/>
+      <c r="H39" s="74"/>
+      <c r="I39" s="74"/>
+      <c r="J39" s="74"/>
+      <c r="K39" s="74"/>
+      <c r="L39" s="74"/>
+      <c r="M39" s="74"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="75" t="s">
+        <v>275</v>
+      </c>
+      <c r="P39" s="75"/>
+      <c r="Q39" s="75"/>
+      <c r="R39" s="75"/>
+      <c r="S39" s="75"/>
+      <c r="T39" s="75"/>
+      <c r="U39" s="75"/>
+      <c r="V39" s="75"/>
+      <c r="W39" s="75"/>
+      <c r="X39" s="75"/>
+      <c r="Y39" s="75"/>
+    </row>
+    <row r="40" spans="3:25" ht="68.099999999999994" customHeight="1">
+      <c r="C40" s="74" t="s">
         <v>266</v>
       </c>
-      <c r="D38" s="132"/>
-      <c r="E38" s="132"/>
-      <c r="F38" s="132"/>
-      <c r="G38" s="132"/>
-      <c r="H38" s="132"/>
-      <c r="I38" s="132"/>
-      <c r="J38" s="132"/>
-      <c r="K38" s="132"/>
-      <c r="L38" s="132"/>
-      <c r="M38" s="132"/>
-      <c r="N38" s="132"/>
-      <c r="O38" s="132" t="s">
+      <c r="D40" s="74"/>
+      <c r="E40" s="74"/>
+      <c r="F40" s="74"/>
+      <c r="G40" s="74"/>
+      <c r="H40" s="74"/>
+      <c r="I40" s="74"/>
+      <c r="J40" s="74"/>
+      <c r="K40" s="74"/>
+      <c r="L40" s="74"/>
+      <c r="M40" s="74"/>
+      <c r="N40" s="74"/>
+      <c r="O40" s="75" t="s">
+        <v>276</v>
+      </c>
+      <c r="P40" s="75"/>
+      <c r="Q40" s="75"/>
+      <c r="R40" s="75"/>
+      <c r="S40" s="75"/>
+      <c r="T40" s="75"/>
+      <c r="U40" s="75"/>
+      <c r="V40" s="75"/>
+      <c r="W40" s="75"/>
+      <c r="X40" s="75"/>
+      <c r="Y40" s="75"/>
+    </row>
+    <row r="41" spans="3:25" ht="68.099999999999994" customHeight="1">
+      <c r="C41" s="74" t="s">
         <v>267</v>
       </c>
-      <c r="P38" s="132"/>
-      <c r="Q38" s="132"/>
-      <c r="R38" s="132"/>
-      <c r="S38" s="132"/>
-      <c r="T38" s="132"/>
-      <c r="U38" s="132"/>
-      <c r="V38" s="132"/>
-      <c r="W38" s="132"/>
-      <c r="X38" s="132"/>
-      <c r="Y38" s="132"/>
-    </row>
-    <row r="39" spans="3:25" ht="68.099999999999994" customHeight="1">
-      <c r="C39" s="132" t="s">
+      <c r="D41" s="74"/>
+      <c r="E41" s="74"/>
+      <c r="F41" s="74"/>
+      <c r="G41" s="74"/>
+      <c r="H41" s="74"/>
+      <c r="I41" s="74"/>
+      <c r="J41" s="74"/>
+      <c r="K41" s="74"/>
+      <c r="L41" s="74"/>
+      <c r="M41" s="74"/>
+      <c r="N41" s="74"/>
+      <c r="O41" s="75" t="s">
+        <v>277</v>
+      </c>
+      <c r="P41" s="75"/>
+      <c r="Q41" s="75"/>
+      <c r="R41" s="75"/>
+      <c r="S41" s="75"/>
+      <c r="T41" s="75"/>
+      <c r="U41" s="75"/>
+      <c r="V41" s="75"/>
+      <c r="W41" s="75"/>
+      <c r="X41" s="75"/>
+      <c r="Y41" s="75"/>
+    </row>
+    <row r="42" spans="3:25" ht="68.099999999999994" customHeight="1">
+      <c r="C42" s="74" t="s">
         <v>268</v>
       </c>
-      <c r="D39" s="132"/>
-      <c r="E39" s="132"/>
-      <c r="F39" s="132"/>
-      <c r="G39" s="132"/>
-      <c r="H39" s="132"/>
-      <c r="I39" s="132"/>
-      <c r="J39" s="132"/>
-      <c r="K39" s="132"/>
-      <c r="L39" s="132"/>
-      <c r="M39" s="132"/>
-      <c r="N39" s="132"/>
-      <c r="O39" s="133" t="s">
+      <c r="D42" s="74"/>
+      <c r="E42" s="74"/>
+      <c r="F42" s="74"/>
+      <c r="G42" s="74"/>
+      <c r="H42" s="74"/>
+      <c r="I42" s="74"/>
+      <c r="J42" s="74"/>
+      <c r="K42" s="74"/>
+      <c r="L42" s="74"/>
+      <c r="M42" s="74"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="75" t="s">
         <v>278</v>
       </c>
-      <c r="P39" s="133"/>
-      <c r="Q39" s="133"/>
-      <c r="R39" s="133"/>
-      <c r="S39" s="133"/>
-      <c r="T39" s="133"/>
-      <c r="U39" s="133"/>
-      <c r="V39" s="133"/>
-      <c r="W39" s="133"/>
-      <c r="X39" s="133"/>
-      <c r="Y39" s="133"/>
-    </row>
-    <row r="40" spans="3:25" ht="68.099999999999994" customHeight="1">
-      <c r="C40" s="132" t="s">
+      <c r="P42" s="75"/>
+      <c r="Q42" s="75"/>
+      <c r="R42" s="75"/>
+      <c r="S42" s="75"/>
+      <c r="T42" s="75"/>
+      <c r="U42" s="75"/>
+      <c r="V42" s="75"/>
+      <c r="W42" s="75"/>
+      <c r="X42" s="75"/>
+      <c r="Y42" s="75"/>
+    </row>
+    <row r="43" spans="3:25" ht="68.099999999999994" customHeight="1">
+      <c r="C43" s="74" t="s">
         <v>269</v>
       </c>
-      <c r="D40" s="132"/>
-      <c r="E40" s="132"/>
-      <c r="F40" s="132"/>
-      <c r="G40" s="132"/>
-      <c r="H40" s="132"/>
-      <c r="I40" s="132"/>
-      <c r="J40" s="132"/>
-      <c r="K40" s="132"/>
-      <c r="L40" s="132"/>
-      <c r="M40" s="132"/>
-      <c r="N40" s="132"/>
-      <c r="O40" s="133" t="s">
+      <c r="D43" s="74"/>
+      <c r="E43" s="74"/>
+      <c r="F43" s="74"/>
+      <c r="G43" s="74"/>
+      <c r="H43" s="74"/>
+      <c r="I43" s="74"/>
+      <c r="J43" s="74"/>
+      <c r="K43" s="74"/>
+      <c r="L43" s="74"/>
+      <c r="M43" s="74"/>
+      <c r="N43" s="74"/>
+      <c r="O43" s="75" t="s">
         <v>279</v>
       </c>
-      <c r="P40" s="133"/>
-      <c r="Q40" s="133"/>
-      <c r="R40" s="133"/>
-      <c r="S40" s="133"/>
-      <c r="T40" s="133"/>
-      <c r="U40" s="133"/>
-      <c r="V40" s="133"/>
-      <c r="W40" s="133"/>
-      <c r="X40" s="133"/>
-      <c r="Y40" s="133"/>
-    </row>
-    <row r="41" spans="3:25" ht="68.099999999999994" customHeight="1">
-      <c r="C41" s="132" t="s">
+      <c r="P43" s="75"/>
+      <c r="Q43" s="75"/>
+      <c r="R43" s="75"/>
+      <c r="S43" s="75"/>
+      <c r="T43" s="75"/>
+      <c r="U43" s="75"/>
+      <c r="V43" s="75"/>
+      <c r="W43" s="75"/>
+      <c r="X43" s="75"/>
+      <c r="Y43" s="75"/>
+    </row>
+    <row r="44" spans="3:25" ht="68.099999999999994" customHeight="1">
+      <c r="C44" s="74" t="s">
         <v>270</v>
       </c>
-      <c r="D41" s="132"/>
-      <c r="E41" s="132"/>
-      <c r="F41" s="132"/>
-      <c r="G41" s="132"/>
-      <c r="H41" s="132"/>
-      <c r="I41" s="132"/>
-      <c r="J41" s="132"/>
-      <c r="K41" s="132"/>
-      <c r="L41" s="132"/>
-      <c r="M41" s="132"/>
-      <c r="N41" s="132"/>
-      <c r="O41" s="133" t="s">
+      <c r="D44" s="74"/>
+      <c r="E44" s="74"/>
+      <c r="F44" s="74"/>
+      <c r="G44" s="74"/>
+      <c r="H44" s="74"/>
+      <c r="I44" s="74"/>
+      <c r="J44" s="74"/>
+      <c r="K44" s="74"/>
+      <c r="L44" s="74"/>
+      <c r="M44" s="74"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="75" t="s">
         <v>280</v>
       </c>
-      <c r="P41" s="133"/>
-      <c r="Q41" s="133"/>
-      <c r="R41" s="133"/>
-      <c r="S41" s="133"/>
-      <c r="T41" s="133"/>
-      <c r="U41" s="133"/>
-      <c r="V41" s="133"/>
-      <c r="W41" s="133"/>
-      <c r="X41" s="133"/>
-      <c r="Y41" s="133"/>
-    </row>
-    <row r="42" spans="3:25" ht="68.099999999999994" customHeight="1">
-      <c r="C42" s="132" t="s">
+      <c r="P44" s="75"/>
+      <c r="Q44" s="75"/>
+      <c r="R44" s="75"/>
+      <c r="S44" s="75"/>
+      <c r="T44" s="75"/>
+      <c r="U44" s="75"/>
+      <c r="V44" s="75"/>
+      <c r="W44" s="75"/>
+      <c r="X44" s="75"/>
+      <c r="Y44" s="75"/>
+    </row>
+    <row r="45" spans="3:25" ht="68.099999999999994" customHeight="1">
+      <c r="C45" s="74" t="s">
         <v>271</v>
       </c>
-      <c r="D42" s="132"/>
-      <c r="E42" s="132"/>
-      <c r="F42" s="132"/>
-      <c r="G42" s="132"/>
-      <c r="H42" s="132"/>
-      <c r="I42" s="132"/>
-      <c r="J42" s="132"/>
-      <c r="K42" s="132"/>
-      <c r="L42" s="132"/>
-      <c r="M42" s="132"/>
-      <c r="N42" s="132"/>
-      <c r="O42" s="133" t="s">
+      <c r="D45" s="74"/>
+      <c r="E45" s="74"/>
+      <c r="F45" s="74"/>
+      <c r="G45" s="74"/>
+      <c r="H45" s="74"/>
+      <c r="I45" s="74"/>
+      <c r="J45" s="74"/>
+      <c r="K45" s="74"/>
+      <c r="L45" s="74"/>
+      <c r="M45" s="74"/>
+      <c r="N45" s="74"/>
+      <c r="O45" s="75" t="s">
         <v>281</v>
       </c>
-      <c r="P42" s="133"/>
-      <c r="Q42" s="133"/>
-      <c r="R42" s="133"/>
-      <c r="S42" s="133"/>
-      <c r="T42" s="133"/>
-      <c r="U42" s="133"/>
-      <c r="V42" s="133"/>
-      <c r="W42" s="133"/>
-      <c r="X42" s="133"/>
-      <c r="Y42" s="133"/>
-    </row>
-    <row r="43" spans="3:25" ht="68.099999999999994" customHeight="1">
-      <c r="C43" s="132" t="s">
+      <c r="P45" s="75"/>
+      <c r="Q45" s="75"/>
+      <c r="R45" s="75"/>
+      <c r="S45" s="75"/>
+      <c r="T45" s="75"/>
+      <c r="U45" s="75"/>
+      <c r="V45" s="75"/>
+      <c r="W45" s="75"/>
+      <c r="X45" s="75"/>
+      <c r="Y45" s="75"/>
+    </row>
+    <row r="46" spans="3:25" ht="68.099999999999994" customHeight="1">
+      <c r="C46" s="74" t="s">
         <v>272</v>
       </c>
-      <c r="D43" s="132"/>
-      <c r="E43" s="132"/>
-      <c r="F43" s="132"/>
-      <c r="G43" s="132"/>
-      <c r="H43" s="132"/>
-      <c r="I43" s="132"/>
-      <c r="J43" s="132"/>
-      <c r="K43" s="132"/>
-      <c r="L43" s="132"/>
-      <c r="M43" s="132"/>
-      <c r="N43" s="132"/>
-      <c r="O43" s="133" t="s">
+      <c r="D46" s="74"/>
+      <c r="E46" s="74"/>
+      <c r="F46" s="74"/>
+      <c r="G46" s="74"/>
+      <c r="H46" s="74"/>
+      <c r="I46" s="74"/>
+      <c r="J46" s="74"/>
+      <c r="K46" s="74"/>
+      <c r="L46" s="74"/>
+      <c r="M46" s="74"/>
+      <c r="N46" s="74"/>
+      <c r="O46" s="75" t="s">
         <v>282</v>
       </c>
-      <c r="P43" s="133"/>
-      <c r="Q43" s="133"/>
-      <c r="R43" s="133"/>
-      <c r="S43" s="133"/>
-      <c r="T43" s="133"/>
-      <c r="U43" s="133"/>
-      <c r="V43" s="133"/>
-      <c r="W43" s="133"/>
-      <c r="X43" s="133"/>
-      <c r="Y43" s="133"/>
-    </row>
-    <row r="44" spans="3:25" ht="68.099999999999994" customHeight="1">
-      <c r="C44" s="132" t="s">
+      <c r="P46" s="75"/>
+      <c r="Q46" s="75"/>
+      <c r="R46" s="75"/>
+      <c r="S46" s="75"/>
+      <c r="T46" s="75"/>
+      <c r="U46" s="75"/>
+      <c r="V46" s="75"/>
+      <c r="W46" s="75"/>
+      <c r="X46" s="75"/>
+      <c r="Y46" s="75"/>
+    </row>
+    <row r="47" spans="3:25" ht="68.099999999999994" customHeight="1">
+      <c r="C47" s="74" t="s">
         <v>273</v>
       </c>
-      <c r="D44" s="132"/>
-      <c r="E44" s="132"/>
-      <c r="F44" s="132"/>
-      <c r="G44" s="132"/>
-      <c r="H44" s="132"/>
-      <c r="I44" s="132"/>
-      <c r="J44" s="132"/>
-      <c r="K44" s="132"/>
-      <c r="L44" s="132"/>
-      <c r="M44" s="132"/>
-      <c r="N44" s="132"/>
-      <c r="O44" s="133" t="s">
+      <c r="D47" s="74"/>
+      <c r="E47" s="74"/>
+      <c r="F47" s="74"/>
+      <c r="G47" s="74"/>
+      <c r="H47" s="74"/>
+      <c r="I47" s="74"/>
+      <c r="J47" s="74"/>
+      <c r="K47" s="74"/>
+      <c r="L47" s="74"/>
+      <c r="M47" s="74"/>
+      <c r="N47" s="74"/>
+      <c r="O47" s="75" t="s">
         <v>283</v>
       </c>
-      <c r="P44" s="133"/>
-      <c r="Q44" s="133"/>
-      <c r="R44" s="133"/>
-      <c r="S44" s="133"/>
-      <c r="T44" s="133"/>
-      <c r="U44" s="133"/>
-      <c r="V44" s="133"/>
-      <c r="W44" s="133"/>
-      <c r="X44" s="133"/>
-      <c r="Y44" s="133"/>
-    </row>
-    <row r="45" spans="3:25" ht="68.099999999999994" customHeight="1">
-      <c r="C45" s="132" t="s">
+      <c r="P47" s="75"/>
+      <c r="Q47" s="75"/>
+      <c r="R47" s="75"/>
+      <c r="S47" s="75"/>
+      <c r="T47" s="75"/>
+      <c r="U47" s="75"/>
+      <c r="V47" s="75"/>
+      <c r="W47" s="75"/>
+      <c r="X47" s="75"/>
+      <c r="Y47" s="75"/>
+    </row>
+    <row r="48" spans="3:25" ht="68.099999999999994" customHeight="1">
+      <c r="C48" s="74" t="s">
         <v>274</v>
       </c>
-      <c r="D45" s="132"/>
-      <c r="E45" s="132"/>
-      <c r="F45" s="132"/>
-      <c r="G45" s="132"/>
-      <c r="H45" s="132"/>
-      <c r="I45" s="132"/>
-      <c r="J45" s="132"/>
-      <c r="K45" s="132"/>
-      <c r="L45" s="132"/>
-      <c r="M45" s="132"/>
-      <c r="N45" s="132"/>
-      <c r="O45" s="133" t="s">
+      <c r="D48" s="74"/>
+      <c r="E48" s="74"/>
+      <c r="F48" s="74"/>
+      <c r="G48" s="74"/>
+      <c r="H48" s="74"/>
+      <c r="I48" s="74"/>
+      <c r="J48" s="74"/>
+      <c r="K48" s="74"/>
+      <c r="L48" s="74"/>
+      <c r="M48" s="74"/>
+      <c r="N48" s="74"/>
+      <c r="O48" s="75" t="s">
         <v>284</v>
       </c>
-      <c r="P45" s="133"/>
-      <c r="Q45" s="133"/>
-      <c r="R45" s="133"/>
-      <c r="S45" s="133"/>
-      <c r="T45" s="133"/>
-      <c r="U45" s="133"/>
-      <c r="V45" s="133"/>
-      <c r="W45" s="133"/>
-      <c r="X45" s="133"/>
-      <c r="Y45" s="133"/>
-    </row>
-    <row r="46" spans="3:25" ht="68.099999999999994" customHeight="1">
-      <c r="C46" s="132" t="s">
-        <v>275</v>
-      </c>
-      <c r="D46" s="132"/>
-      <c r="E46" s="132"/>
-      <c r="F46" s="132"/>
-      <c r="G46" s="132"/>
-      <c r="H46" s="132"/>
-      <c r="I46" s="132"/>
-      <c r="J46" s="132"/>
-      <c r="K46" s="132"/>
-      <c r="L46" s="132"/>
-      <c r="M46" s="132"/>
-      <c r="N46" s="132"/>
-      <c r="O46" s="133" t="s">
-        <v>285</v>
-      </c>
-      <c r="P46" s="133"/>
-      <c r="Q46" s="133"/>
-      <c r="R46" s="133"/>
-      <c r="S46" s="133"/>
-      <c r="T46" s="133"/>
-      <c r="U46" s="133"/>
-      <c r="V46" s="133"/>
-      <c r="W46" s="133"/>
-      <c r="X46" s="133"/>
-      <c r="Y46" s="133"/>
-    </row>
-    <row r="47" spans="3:25" ht="68.099999999999994" customHeight="1">
-      <c r="C47" s="132" t="s">
-        <v>276</v>
-      </c>
-      <c r="D47" s="132"/>
-      <c r="E47" s="132"/>
-      <c r="F47" s="132"/>
-      <c r="G47" s="132"/>
-      <c r="H47" s="132"/>
-      <c r="I47" s="132"/>
-      <c r="J47" s="132"/>
-      <c r="K47" s="132"/>
-      <c r="L47" s="132"/>
-      <c r="M47" s="132"/>
-      <c r="N47" s="132"/>
-      <c r="O47" s="133" t="s">
-        <v>286</v>
-      </c>
-      <c r="P47" s="133"/>
-      <c r="Q47" s="133"/>
-      <c r="R47" s="133"/>
-      <c r="S47" s="133"/>
-      <c r="T47" s="133"/>
-      <c r="U47" s="133"/>
-      <c r="V47" s="133"/>
-      <c r="W47" s="133"/>
-      <c r="X47" s="133"/>
-      <c r="Y47" s="133"/>
-    </row>
-    <row r="48" spans="3:25" ht="68.099999999999994" customHeight="1">
-      <c r="C48" s="132" t="s">
-        <v>277</v>
-      </c>
-      <c r="D48" s="132"/>
-      <c r="E48" s="132"/>
-      <c r="F48" s="132"/>
-      <c r="G48" s="132"/>
-      <c r="H48" s="132"/>
-      <c r="I48" s="132"/>
-      <c r="J48" s="132"/>
-      <c r="K48" s="132"/>
-      <c r="L48" s="132"/>
-      <c r="M48" s="132"/>
-      <c r="N48" s="132"/>
-      <c r="O48" s="133" t="s">
-        <v>287</v>
-      </c>
-      <c r="P48" s="133"/>
-      <c r="Q48" s="133"/>
-      <c r="R48" s="133"/>
-      <c r="S48" s="133"/>
-      <c r="T48" s="133"/>
-      <c r="U48" s="133"/>
-      <c r="V48" s="133"/>
-      <c r="W48" s="133"/>
-      <c r="X48" s="133"/>
-      <c r="Y48" s="133"/>
+      <c r="P48" s="75"/>
+      <c r="Q48" s="75"/>
+      <c r="R48" s="75"/>
+      <c r="S48" s="75"/>
+      <c r="T48" s="75"/>
+      <c r="U48" s="75"/>
+      <c r="V48" s="75"/>
+      <c r="W48" s="75"/>
+      <c r="X48" s="75"/>
+      <c r="Y48" s="75"/>
     </row>
   </sheetData>
-  <mergeCells count="69">
-    <mergeCell ref="C47:N47"/>
-    <mergeCell ref="O47:Y47"/>
-    <mergeCell ref="C48:N48"/>
-    <mergeCell ref="O48:Y48"/>
-    <mergeCell ref="C44:N44"/>
-    <mergeCell ref="O44:Y44"/>
-    <mergeCell ref="C45:N45"/>
-    <mergeCell ref="O45:Y45"/>
-    <mergeCell ref="C46:N46"/>
-    <mergeCell ref="O46:Y46"/>
-    <mergeCell ref="C41:N41"/>
-    <mergeCell ref="O41:Y41"/>
-    <mergeCell ref="C42:N42"/>
-    <mergeCell ref="O42:Y42"/>
-    <mergeCell ref="C43:N43"/>
-    <mergeCell ref="O43:Y43"/>
-    <mergeCell ref="O38:Y38"/>
-    <mergeCell ref="C38:N38"/>
-    <mergeCell ref="C39:N39"/>
-    <mergeCell ref="O39:Y39"/>
-    <mergeCell ref="C40:N40"/>
-    <mergeCell ref="O40:Y40"/>
-    <mergeCell ref="Y1:Z1"/>
-    <mergeCell ref="AA1:AC1"/>
-    <mergeCell ref="AD1:AF1"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="K1:Q1"/>
-    <mergeCell ref="R1:X1"/>
-    <mergeCell ref="A2:J3"/>
-    <mergeCell ref="K2:Q3"/>
-    <mergeCell ref="R2:X3"/>
+  <mergeCells count="67">
+    <mergeCell ref="E2:R3"/>
+    <mergeCell ref="E1:R1"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D3"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:S19"/>
+    <mergeCell ref="D20:S20"/>
+    <mergeCell ref="D21:S21"/>
+    <mergeCell ref="D22:S22"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D14:S14"/>
+    <mergeCell ref="D15:S15"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="U3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="S2:T2"/>
     <mergeCell ref="D18:S18"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="D16:S16"/>
@@ -6076,31 +6054,31 @@
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="D12:S12"/>
     <mergeCell ref="D13:S13"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="AD2:AF2"/>
-    <mergeCell ref="Y3:Z3"/>
-    <mergeCell ref="AA3:AC3"/>
-    <mergeCell ref="AD3:AF3"/>
-    <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="D14:S14"/>
-    <mergeCell ref="D15:S15"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D20:S20"/>
-    <mergeCell ref="D21:S21"/>
-    <mergeCell ref="D22:S22"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:S19"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="U1:W1"/>
+    <mergeCell ref="X1:Z1"/>
+    <mergeCell ref="O38:Y38"/>
+    <mergeCell ref="C38:N38"/>
+    <mergeCell ref="C39:N39"/>
+    <mergeCell ref="O39:Y39"/>
+    <mergeCell ref="C40:N40"/>
+    <mergeCell ref="O40:Y40"/>
+    <mergeCell ref="C41:N41"/>
+    <mergeCell ref="O41:Y41"/>
+    <mergeCell ref="C42:N42"/>
+    <mergeCell ref="O42:Y42"/>
+    <mergeCell ref="C43:N43"/>
+    <mergeCell ref="O43:Y43"/>
+    <mergeCell ref="C47:N47"/>
+    <mergeCell ref="O47:Y47"/>
+    <mergeCell ref="C48:N48"/>
+    <mergeCell ref="O48:Y48"/>
+    <mergeCell ref="C44:N44"/>
+    <mergeCell ref="O44:Y44"/>
+    <mergeCell ref="C45:N45"/>
+    <mergeCell ref="O45:Y45"/>
+    <mergeCell ref="C46:N46"/>
+    <mergeCell ref="O46:Y46"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6109,183 +6087,445 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95590121-BC4B-4D68-B73E-610F888E8B68}">
+  <dimension ref="A1:R41"/>
+  <sheetFormatPr defaultColWidth="4.42578125" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.5703125" customWidth="1"/>
+    <col min="17" max="17" width="4.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="15.75" thickBot="1">
+      <c r="A1" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="99" t="s">
+        <v>217</v>
+      </c>
+      <c r="C1" s="100"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="125" t="s">
+        <v>286</v>
+      </c>
+      <c r="F1" s="126"/>
+      <c r="G1" s="99" t="s">
+        <v>218</v>
+      </c>
+      <c r="H1" s="100"/>
+      <c r="I1" s="100"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="86" t="s">
+        <v>210</v>
+      </c>
+      <c r="L1" s="127"/>
+      <c r="M1" s="87"/>
+      <c r="N1" s="99" t="s">
+        <v>219</v>
+      </c>
+      <c r="O1" s="101"/>
+      <c r="P1" s="85">
+        <v>45931</v>
+      </c>
+      <c r="Q1" s="85"/>
+      <c r="R1" s="85"/>
+    </row>
+    <row r="2" spans="1:18" ht="15.75" thickBot="1">
+      <c r="B2" s="99" t="s">
+        <v>220</v>
+      </c>
+      <c r="C2" s="100"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="128">
+        <v>0</v>
+      </c>
+      <c r="F2" s="129"/>
+      <c r="G2" s="99" t="s">
+        <v>221</v>
+      </c>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="101"/>
+      <c r="K2" s="86" t="s">
+        <v>210</v>
+      </c>
+      <c r="L2" s="127"/>
+      <c r="M2" s="87"/>
+      <c r="N2" s="99" t="s">
+        <v>222</v>
+      </c>
+      <c r="O2" s="101"/>
+      <c r="P2" s="85">
+        <v>45968</v>
+      </c>
+      <c r="Q2" s="85"/>
+      <c r="R2" s="85"/>
+    </row>
+    <row r="4" spans="1:18">
+      <c r="C4" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="18">
+      <c r="C6" s="57" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
+      <c r="C7" s="18" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="C8" s="18" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
+      <c r="C9" s="18" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="C10" s="18" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="C11" s="18" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="C12" s="18" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="18">
+      <c r="C14" s="57" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
+      <c r="C15" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="C16" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3">
+      <c r="C19" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="21" spans="3:3" ht="18">
+      <c r="C21" s="57" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="22" spans="3:3">
+      <c r="C22" s="18" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="23" spans="3:3">
+      <c r="C23" s="18" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="24" spans="3:3">
+      <c r="C24" s="18" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="25" spans="3:3">
+      <c r="C25" s="18" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="26" spans="3:3">
+      <c r="C26" s="18" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="28" spans="3:3" ht="18">
+      <c r="C28" s="57" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="29" spans="3:3">
+      <c r="C29" s="18" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="30" spans="3:3">
+      <c r="C30" s="18" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="31" spans="3:3">
+      <c r="C31" s="18" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="32" spans="3:3">
+      <c r="C32" s="18" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="34" spans="3:3" ht="18">
+      <c r="C34" s="57" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="35" spans="3:3">
+      <c r="C35" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="36" spans="3:3">
+      <c r="C36" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="37" spans="3:3">
+      <c r="C37" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="38" spans="3:3">
+      <c r="C38" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="40" spans="3:3" ht="18">
+      <c r="C40" s="57" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="41" spans="3:3">
+      <c r="C41" t="s">
+        <v>327</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:R1"/>
+    <mergeCell ref="P2:R2"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="N2:O2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Summary!A1" display="Summary" xr:uid="{787EF59B-4D9C-40F3-9D46-32BA474BC12D}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="16.5703125" customWidth="1"/>
     <col min="3" max="3" width="71.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="77.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.7109375" customWidth="1"/>
+    <col min="10" max="10" width="5.5703125" customWidth="1"/>
+    <col min="11" max="11" width="3.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" customHeight="1" thickBot="1">
+    <row r="1" spans="1:11" ht="15.75" customHeight="1" thickBot="1">
       <c r="A1" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="126" t="s">
-        <v>219</v>
+        <v>5</v>
+      </c>
+      <c r="B1" s="54" t="s">
+        <v>217</v>
       </c>
       <c r="C1" s="52" t="s">
-        <v>262</v>
-      </c>
-      <c r="D1" s="127" t="s">
-        <v>220</v>
+        <v>259</v>
+      </c>
+      <c r="D1" s="55" t="s">
+        <v>218</v>
       </c>
       <c r="E1" s="48" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F1" s="49"/>
       <c r="G1" s="50" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H1" s="51"/>
-      <c r="I1" s="115">
-        <v>45750</v>
-      </c>
-      <c r="J1" s="116"/>
-    </row>
-    <row r="2" spans="1:10" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B2" s="126" t="s">
-        <v>222</v>
+      <c r="I1" s="85">
+        <v>45931</v>
+      </c>
+      <c r="J1" s="85"/>
+      <c r="K1" s="85"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" customHeight="1" thickBot="1">
+      <c r="B2" s="54" t="s">
+        <v>220</v>
       </c>
       <c r="C2" s="53">
         <v>0</v>
       </c>
-      <c r="D2" s="127" t="s">
-        <v>223</v>
+      <c r="D2" s="55" t="s">
+        <v>221</v>
       </c>
       <c r="E2" s="48" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F2" s="49"/>
       <c r="G2" s="50" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H2" s="51"/>
-      <c r="I2" s="115">
-        <v>45019</v>
-      </c>
-      <c r="J2" s="116"/>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="I2" s="85">
+        <v>45968</v>
+      </c>
+      <c r="J2" s="85"/>
+      <c r="K2" s="85"/>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="12"/>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:11">
       <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="B7" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C7" s="22" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="B7" s="22" t="s">
+      <c r="D7" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="22" t="s">
+    </row>
+    <row r="8" spans="1:11">
+      <c r="B8" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="C8" s="73" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="B8" s="84" t="s">
+      <c r="D8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="64" t="s">
+    </row>
+    <row r="9" spans="1:11">
+      <c r="B9" s="89"/>
+      <c r="C9" s="73"/>
+      <c r="D9" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="8" t="s">
+    </row>
+    <row r="10" spans="1:11" ht="45">
+      <c r="B10" s="9" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="B9" s="84"/>
-      <c r="C9" s="64"/>
-      <c r="D9" s="8" t="s">
+      <c r="C10" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="10" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="45">
-      <c r="B10" s="9" t="s">
+    <row r="11" spans="1:11">
+      <c r="B11" s="95" t="s">
+        <v>216</v>
+      </c>
+      <c r="C11" s="97" t="s">
+        <v>214</v>
+      </c>
+      <c r="D11" s="97" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="B12" s="96"/>
+      <c r="C12" s="98"/>
+      <c r="D12" s="98"/>
+    </row>
+    <row r="13" spans="1:11" ht="30" customHeight="1">
+      <c r="B13" s="92" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="10" t="s">
+      <c r="C13" s="73" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="B11" s="88" t="s">
-        <v>218</v>
-      </c>
-      <c r="C11" s="90" t="s">
-        <v>216</v>
-      </c>
-      <c r="D11" s="90" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="B12" s="89"/>
-      <c r="C12" s="91"/>
-      <c r="D12" s="91"/>
-    </row>
-    <row r="13" spans="1:10" ht="30" customHeight="1">
-      <c r="B13" s="94" t="s">
+      <c r="D13" s="73" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="64" t="s">
+    </row>
+    <row r="14" spans="1:11">
+      <c r="B14" s="92"/>
+      <c r="C14" s="73"/>
+      <c r="D14" s="73"/>
+    </row>
+    <row r="15" spans="1:11" ht="45" customHeight="1">
+      <c r="B15" s="89" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="64" t="s">
+      <c r="C15" s="90" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="B14" s="94"/>
-      <c r="C14" s="64"/>
-      <c r="D14" s="64"/>
-    </row>
-    <row r="15" spans="1:10" ht="45" customHeight="1">
-      <c r="B15" s="84" t="s">
+      <c r="D15" s="73" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="87" t="s">
+    </row>
+    <row r="16" spans="1:11">
+      <c r="B16" s="89"/>
+      <c r="C16" s="90"/>
+      <c r="D16" s="73"/>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="B17" s="89"/>
+      <c r="C17" s="90"/>
+      <c r="D17" s="73"/>
+    </row>
+    <row r="18" spans="2:4" ht="30" customHeight="1">
+      <c r="B18" s="93" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="64" t="s">
+      <c r="C18" s="90" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="B16" s="84"/>
-      <c r="C16" s="87"/>
-      <c r="D16" s="64"/>
-    </row>
-    <row r="17" spans="2:4">
-      <c r="B17" s="84"/>
-      <c r="C17" s="87"/>
-      <c r="D17" s="64"/>
-    </row>
-    <row r="18" spans="2:4" ht="30" customHeight="1">
-      <c r="B18" s="85" t="s">
+      <c r="D18" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="87" t="s">
-        <v>35</v>
-      </c>
-      <c r="D18" s="64" t="s">
-        <v>36</v>
-      </c>
     </row>
     <row r="19" spans="2:4">
-      <c r="B19" s="86"/>
-      <c r="C19" s="93"/>
-      <c r="D19" s="64"/>
+      <c r="B19" s="94"/>
+      <c r="C19" s="91"/>
+      <c r="D19" s="73"/>
     </row>
     <row r="20" spans="2:4">
       <c r="B20" s="28"/>
@@ -6294,50 +6534,51 @@
     </row>
     <row r="21" spans="2:4">
       <c r="C21" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="22" spans="2:4">
       <c r="B22" s="27" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C22" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="23" spans="2:4">
       <c r="C23" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="24" spans="2:4">
       <c r="C24" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="25" spans="2:4" ht="15" customHeight="1">
-      <c r="C25" s="92" t="s">
-        <v>204</v>
-      </c>
-      <c r="D25" s="92"/>
+      <c r="C25" s="88" t="s">
+        <v>202</v>
+      </c>
+      <c r="D25" s="88"/>
     </row>
     <row r="26" spans="2:4">
-      <c r="C26" s="92"/>
-      <c r="D26" s="92"/>
+      <c r="C26" s="88"/>
+      <c r="D26" s="88"/>
     </row>
     <row r="27" spans="2:4">
-      <c r="C27" s="92"/>
-      <c r="D27" s="92"/>
+      <c r="C27" s="88"/>
+      <c r="D27" s="88"/>
     </row>
     <row r="28" spans="2:4">
       <c r="C28" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="I2:K2"/>
     <mergeCell ref="C25:D27"/>
     <mergeCell ref="B15:B17"/>
     <mergeCell ref="C18:C19"/>
@@ -6352,7 +6593,6 @@
     <mergeCell ref="C15:C17"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Summary!A1" display="Summary" xr:uid="{1A2015EB-03FE-4B7E-8F51-F773BCFC5BDD}"/>
@@ -6362,264 +6602,269 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:N43"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col min="5" max="5" width="35.140625" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+    <col min="14" max="14" width="4.42578125" customWidth="1"/>
+    <col min="15" max="15" width="5.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.75" thickBot="1">
+    <row r="1" spans="1:15" ht="15.75" thickBot="1">
       <c r="A1" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="117" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="99" t="s">
+        <v>217</v>
+      </c>
+      <c r="C1" s="100"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="52" t="s">
+        <v>258</v>
+      </c>
+      <c r="F1" s="99" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1" s="100"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="86" t="s">
+        <v>210</v>
+      </c>
+      <c r="J1" s="87"/>
+      <c r="K1" s="99" t="s">
         <v>219</v>
       </c>
-      <c r="C1" s="118"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="52" t="s">
-        <v>261</v>
-      </c>
-      <c r="F1" s="117" t="s">
+      <c r="L1" s="101"/>
+      <c r="M1" s="85">
+        <v>45931</v>
+      </c>
+      <c r="N1" s="85"/>
+      <c r="O1" s="85"/>
+    </row>
+    <row r="2" spans="1:15" ht="15.75" thickBot="1">
+      <c r="B2" s="99" t="s">
         <v>220</v>
       </c>
-      <c r="G1" s="118"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="115" t="s">
-        <v>212</v>
-      </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="117" t="s">
-        <v>221</v>
-      </c>
-      <c r="L1" s="119"/>
-      <c r="M1" s="115">
-        <v>45750</v>
-      </c>
-      <c r="N1" s="116"/>
-    </row>
-    <row r="2" spans="1:14" ht="15.75" thickBot="1">
-      <c r="B2" s="117" t="s">
-        <v>222</v>
-      </c>
-      <c r="C2" s="118"/>
-      <c r="D2" s="119"/>
+      <c r="C2" s="100"/>
+      <c r="D2" s="101"/>
       <c r="E2" s="53">
         <v>0</v>
       </c>
-      <c r="F2" s="117" t="s">
-        <v>223</v>
-      </c>
-      <c r="G2" s="118"/>
-      <c r="H2" s="119"/>
-      <c r="I2" s="115" t="s">
-        <v>212</v>
-      </c>
-      <c r="J2" s="116"/>
-      <c r="K2" s="117" t="s">
-        <v>224</v>
-      </c>
-      <c r="L2" s="119"/>
-      <c r="M2" s="115">
-        <v>45750</v>
-      </c>
-      <c r="N2" s="116"/>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="F2" s="99" t="s">
+        <v>221</v>
+      </c>
+      <c r="G2" s="100"/>
+      <c r="H2" s="101"/>
+      <c r="I2" s="86" t="s">
+        <v>210</v>
+      </c>
+      <c r="J2" s="87"/>
+      <c r="K2" s="99" t="s">
+        <v>222</v>
+      </c>
+      <c r="L2" s="101"/>
+      <c r="M2" s="85">
+        <v>45968</v>
+      </c>
+      <c r="N2" s="85"/>
+      <c r="O2" s="85"/>
+    </row>
+    <row r="4" spans="1:15">
       <c r="D4" s="24" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="60">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="60">
       <c r="D5" s="47" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
     </row>
-    <row r="7" spans="1:14" ht="75">
+    <row r="7" spans="1:15" ht="75">
       <c r="D7" s="47" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="23.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="23.25">
       <c r="D9" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E9" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="C10" s="88" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="88"/>
+      <c r="E10" s="88"/>
+      <c r="F10" s="88"/>
+      <c r="G10" s="88"/>
+      <c r="H10" s="88"/>
+      <c r="I10" s="88"/>
+      <c r="J10" s="88"/>
+      <c r="K10" s="88"/>
+      <c r="L10" s="88"/>
+      <c r="M10" s="88"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="C11" s="88"/>
+      <c r="D11" s="88"/>
+      <c r="E11" s="88"/>
+      <c r="F11" s="88"/>
+      <c r="G11" s="88"/>
+      <c r="H11" s="88"/>
+      <c r="I11" s="88"/>
+      <c r="J11" s="88"/>
+      <c r="K11" s="88"/>
+      <c r="L11" s="88"/>
+      <c r="M11" s="88"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="D12" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
-      <c r="C10" s="92" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="92"/>
-      <c r="E10" s="92"/>
-      <c r="F10" s="92"/>
-      <c r="G10" s="92"/>
-      <c r="H10" s="92"/>
-      <c r="I10" s="92"/>
-      <c r="J10" s="92"/>
-      <c r="K10" s="92"/>
-      <c r="L10" s="92"/>
-      <c r="M10" s="92"/>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="C11" s="92"/>
-      <c r="D11" s="92"/>
-      <c r="E11" s="92"/>
-      <c r="F11" s="92"/>
-      <c r="G11" s="92"/>
-      <c r="H11" s="92"/>
-      <c r="I11" s="92"/>
-      <c r="J11" s="92"/>
-      <c r="K11" s="92"/>
-      <c r="L11" s="92"/>
-      <c r="M11" s="92"/>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="D12" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:15">
       <c r="D13" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="D14" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="4:13">
       <c r="D20" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="4:13">
       <c r="D25" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="4:13">
       <c r="D26" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="4:13" ht="15" customHeight="1">
       <c r="D27" t="s">
-        <v>50</v>
-      </c>
-      <c r="E27" s="92" t="s">
-        <v>51</v>
-      </c>
-      <c r="F27" s="92"/>
-      <c r="G27" s="92"/>
-      <c r="H27" s="92"/>
-      <c r="I27" s="92"/>
-      <c r="J27" s="92"/>
-      <c r="K27" s="92"/>
-      <c r="L27" s="92"/>
-      <c r="M27" s="92"/>
+        <v>48</v>
+      </c>
+      <c r="E27" s="88" t="s">
+        <v>49</v>
+      </c>
+      <c r="F27" s="88"/>
+      <c r="G27" s="88"/>
+      <c r="H27" s="88"/>
+      <c r="I27" s="88"/>
+      <c r="J27" s="88"/>
+      <c r="K27" s="88"/>
+      <c r="L27" s="88"/>
+      <c r="M27" s="88"/>
     </row>
     <row r="28" spans="4:13">
-      <c r="E28" s="92"/>
-      <c r="F28" s="92"/>
-      <c r="G28" s="92"/>
-      <c r="H28" s="92"/>
-      <c r="I28" s="92"/>
-      <c r="J28" s="92"/>
-      <c r="K28" s="92"/>
-      <c r="L28" s="92"/>
-      <c r="M28" s="92"/>
+      <c r="E28" s="88"/>
+      <c r="F28" s="88"/>
+      <c r="G28" s="88"/>
+      <c r="H28" s="88"/>
+      <c r="I28" s="88"/>
+      <c r="J28" s="88"/>
+      <c r="K28" s="88"/>
+      <c r="L28" s="88"/>
+      <c r="M28" s="88"/>
     </row>
     <row r="29" spans="4:13">
-      <c r="E29" s="92"/>
-      <c r="F29" s="92"/>
-      <c r="G29" s="92"/>
-      <c r="H29" s="92"/>
-      <c r="I29" s="92"/>
-      <c r="J29" s="92"/>
-      <c r="K29" s="92"/>
-      <c r="L29" s="92"/>
-      <c r="M29" s="92"/>
+      <c r="E29" s="88"/>
+      <c r="F29" s="88"/>
+      <c r="G29" s="88"/>
+      <c r="H29" s="88"/>
+      <c r="I29" s="88"/>
+      <c r="J29" s="88"/>
+      <c r="K29" s="88"/>
+      <c r="L29" s="88"/>
+      <c r="M29" s="88"/>
     </row>
     <row r="30" spans="4:13">
       <c r="D30" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="4:13">
       <c r="D32" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" spans="4:5" ht="23.25">
       <c r="D34" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E34" s="23" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="35" spans="4:5" outlineLevel="1">
       <c r="D35" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="36" spans="4:5" outlineLevel="1">
       <c r="D36" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="37" spans="4:5" outlineLevel="1">
       <c r="D37" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="38" spans="4:5" outlineLevel="1">
       <c r="D38" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="39" spans="4:5" outlineLevel="1">
       <c r="D39" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="40" spans="4:5" outlineLevel="1">
       <c r="D40" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="41" spans="4:5" outlineLevel="1">
       <c r="D41" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="42" spans="4:5" outlineLevel="1">
       <c r="D42" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="43" spans="4:5" outlineLevel="1">
       <c r="D43" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -6630,12 +6875,12 @@
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="K1:L1"/>
-    <mergeCell ref="M1:N1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="M2:O2"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Summary!A1" display="Summary" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
@@ -6646,303 +6891,308 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:N54"/>
+  <dimension ref="A1:O54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="5" max="5" width="14.28515625" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+    <col min="14" max="14" width="5.28515625" customWidth="1"/>
+    <col min="15" max="15" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="29.25" thickBot="1">
+    <row r="1" spans="1:15" ht="29.25" thickBot="1">
       <c r="A1" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="117" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="99" t="s">
+        <v>217</v>
+      </c>
+      <c r="C1" s="100"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="99" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1" s="100"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="86" t="s">
+        <v>210</v>
+      </c>
+      <c r="J1" s="87"/>
+      <c r="K1" s="99" t="s">
         <v>219</v>
       </c>
-      <c r="C1" s="118"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="52" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="117" t="s">
+      <c r="L1" s="101"/>
+      <c r="M1" s="85">
+        <v>45931</v>
+      </c>
+      <c r="N1" s="85"/>
+      <c r="O1" s="85"/>
+    </row>
+    <row r="2" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A2" s="12"/>
+      <c r="B2" s="99" t="s">
         <v>220</v>
       </c>
-      <c r="G1" s="118"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="115" t="s">
-        <v>212</v>
-      </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="117" t="s">
-        <v>221</v>
-      </c>
-      <c r="L1" s="119"/>
-      <c r="M1" s="115">
-        <v>45750</v>
-      </c>
-      <c r="N1" s="116"/>
-    </row>
-    <row r="2" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A2" s="12"/>
-      <c r="B2" s="117" t="s">
-        <v>222</v>
-      </c>
-      <c r="C2" s="118"/>
-      <c r="D2" s="119"/>
+      <c r="C2" s="100"/>
+      <c r="D2" s="101"/>
       <c r="E2" s="53">
         <v>0</v>
       </c>
-      <c r="F2" s="117" t="s">
-        <v>223</v>
-      </c>
-      <c r="G2" s="118"/>
-      <c r="H2" s="119"/>
-      <c r="I2" s="115" t="s">
-        <v>212</v>
-      </c>
-      <c r="J2" s="116"/>
-      <c r="K2" s="117" t="s">
-        <v>224</v>
-      </c>
-      <c r="L2" s="119"/>
-      <c r="M2" s="115">
-        <v>45750</v>
-      </c>
-      <c r="N2" s="116"/>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="F2" s="99" t="s">
+        <v>221</v>
+      </c>
+      <c r="G2" s="100"/>
+      <c r="H2" s="101"/>
+      <c r="I2" s="86" t="s">
+        <v>210</v>
+      </c>
+      <c r="J2" s="87"/>
+      <c r="K2" s="99" t="s">
+        <v>222</v>
+      </c>
+      <c r="L2" s="101"/>
+      <c r="M2" s="85">
+        <v>45968</v>
+      </c>
+      <c r="N2" s="85"/>
+      <c r="O2" s="85"/>
+    </row>
+    <row r="4" spans="1:15">
       <c r="B4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="B6" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
-      <c r="B6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:15">
       <c r="B8" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="B9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="B10" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
-      <c r="B9" t="s">
+    <row r="11" spans="1:15">
+      <c r="B11" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
-      <c r="B10" t="s">
+    <row r="12" spans="1:15">
+      <c r="B12" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
-      <c r="B11" t="s">
+    <row r="13" spans="1:15">
+      <c r="B13" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
-      <c r="B12" t="s">
+    <row r="14" spans="1:15">
+      <c r="B14" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
-      <c r="B13" t="s">
+    <row r="15" spans="1:15">
+      <c r="B15" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="B14" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="B15" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="2:2" ht="15.75" thickBot="1"/>
     <row r="23" spans="2:2" ht="15.75" thickBot="1">
       <c r="B23" s="20" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="2:2" ht="15.75" thickBot="1">
       <c r="B24" s="20" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="2:2">
       <c r="B26" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="2:2" ht="15.75" thickBot="1">
       <c r="B28" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="2:2" ht="15.75" thickBot="1">
       <c r="B29" s="21" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" spans="2:2">
       <c r="B33" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36" spans="2:2">
       <c r="B36" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="38" spans="2:2">
       <c r="B38" s="19" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39" spans="2:2">
       <c r="B39" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40" spans="2:2">
       <c r="B40" s="7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="2:2">
       <c r="B41" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" s="7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="2:2">
       <c r="B43" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45" spans="2:2">
       <c r="B45" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="46" spans="2:2">
       <c r="B46" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="47" spans="2:2">
       <c r="B47" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="49" spans="2:2">
       <c r="B49" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="51" spans="2:2">
       <c r="B51" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="52" spans="2:2">
       <c r="B52" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="53" spans="2:2">
       <c r="B53" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="54" spans="2:2">
       <c r="B54" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:O2"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="K1:L1"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="M1:O1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Summary!A1" display="Summary" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
@@ -6953,349 +7203,352 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:Q65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="14" max="14" width="12.42578125" customWidth="1"/>
+    <col min="13" max="14" width="5.5703125" customWidth="1"/>
+    <col min="15" max="15" width="4.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" thickBot="1">
       <c r="A1" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="117" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="99" t="s">
+        <v>217</v>
+      </c>
+      <c r="C1" s="100"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="52" t="s">
+        <v>257</v>
+      </c>
+      <c r="F1" s="99" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1" s="100"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="86" t="s">
+        <v>210</v>
+      </c>
+      <c r="J1" s="87"/>
+      <c r="K1" s="99" t="s">
         <v>219</v>
       </c>
-      <c r="C1" s="118"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="52" t="s">
-        <v>260</v>
-      </c>
-      <c r="F1" s="117" t="s">
+      <c r="L1" s="101"/>
+      <c r="M1" s="85">
+        <v>45931</v>
+      </c>
+      <c r="N1" s="85"/>
+      <c r="O1" s="85"/>
+    </row>
+    <row r="2" spans="1:17" ht="15.75" thickBot="1">
+      <c r="B2" s="99" t="s">
         <v>220</v>
       </c>
-      <c r="G1" s="118"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="115" t="s">
-        <v>212</v>
-      </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="117" t="s">
-        <v>221</v>
-      </c>
-      <c r="L1" s="119"/>
-      <c r="M1" s="115">
-        <v>45750</v>
-      </c>
-      <c r="N1" s="116"/>
-    </row>
-    <row r="2" spans="1:17" ht="15.75" thickBot="1">
-      <c r="B2" s="117" t="s">
-        <v>222</v>
-      </c>
-      <c r="C2" s="118"/>
-      <c r="D2" s="119"/>
+      <c r="C2" s="100"/>
+      <c r="D2" s="101"/>
       <c r="E2" s="53">
         <v>0</v>
       </c>
-      <c r="F2" s="117" t="s">
-        <v>223</v>
-      </c>
-      <c r="G2" s="118"/>
-      <c r="H2" s="119"/>
-      <c r="I2" s="115" t="s">
-        <v>212</v>
-      </c>
-      <c r="J2" s="116"/>
-      <c r="K2" s="117" t="s">
-        <v>224</v>
-      </c>
-      <c r="L2" s="119"/>
-      <c r="M2" s="115">
-        <v>45750</v>
-      </c>
-      <c r="N2" s="116"/>
+      <c r="F2" s="99" t="s">
+        <v>221</v>
+      </c>
+      <c r="G2" s="100"/>
+      <c r="H2" s="101"/>
+      <c r="I2" s="86" t="s">
+        <v>210</v>
+      </c>
+      <c r="J2" s="87"/>
+      <c r="K2" s="99" t="s">
+        <v>222</v>
+      </c>
+      <c r="L2" s="101"/>
+      <c r="M2" s="85">
+        <v>45968</v>
+      </c>
+      <c r="N2" s="85"/>
+      <c r="O2" s="85"/>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="12"/>
     </row>
     <row r="4" spans="1:17">
       <c r="B4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:17">
-      <c r="D5" s="95" t="s">
-        <v>98</v>
-      </c>
-      <c r="E5" s="95"/>
-      <c r="F5" s="95"/>
-      <c r="G5" s="95"/>
-      <c r="H5" s="95"/>
-      <c r="I5" s="95"/>
-      <c r="J5" s="95"/>
-      <c r="K5" s="95"/>
-      <c r="L5" s="95"/>
-      <c r="M5" s="95"/>
-      <c r="N5" s="95"/>
-      <c r="O5" s="95"/>
+      <c r="D5" s="108" t="s">
+        <v>96</v>
+      </c>
+      <c r="E5" s="108"/>
+      <c r="F5" s="108"/>
+      <c r="G5" s="108"/>
+      <c r="H5" s="108"/>
+      <c r="I5" s="108"/>
+      <c r="J5" s="108"/>
+      <c r="K5" s="108"/>
+      <c r="L5" s="108"/>
+      <c r="M5" s="108"/>
+      <c r="N5" s="108"/>
+      <c r="O5" s="108"/>
     </row>
     <row r="6" spans="1:17">
-      <c r="D6" s="95"/>
-      <c r="E6" s="95"/>
-      <c r="F6" s="95"/>
-      <c r="G6" s="95"/>
-      <c r="H6" s="95"/>
-      <c r="I6" s="95"/>
-      <c r="J6" s="95"/>
-      <c r="K6" s="95"/>
-      <c r="L6" s="95"/>
-      <c r="M6" s="95"/>
-      <c r="N6" s="95"/>
-      <c r="O6" s="95"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="108"/>
+      <c r="F6" s="108"/>
+      <c r="G6" s="108"/>
+      <c r="H6" s="108"/>
+      <c r="I6" s="108"/>
+      <c r="J6" s="108"/>
+      <c r="K6" s="108"/>
+      <c r="L6" s="108"/>
+      <c r="M6" s="108"/>
+      <c r="N6" s="108"/>
+      <c r="O6" s="108"/>
     </row>
     <row r="7" spans="1:17">
-      <c r="D7" s="95"/>
-      <c r="E7" s="95"/>
-      <c r="F7" s="95"/>
-      <c r="G7" s="95"/>
-      <c r="H7" s="95"/>
-      <c r="I7" s="95"/>
-      <c r="J7" s="95"/>
-      <c r="K7" s="95"/>
-      <c r="L7" s="95"/>
-      <c r="M7" s="95"/>
-      <c r="N7" s="95"/>
-      <c r="O7" s="95"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="108"/>
+      <c r="F7" s="108"/>
+      <c r="G7" s="108"/>
+      <c r="H7" s="108"/>
+      <c r="I7" s="108"/>
+      <c r="J7" s="108"/>
+      <c r="K7" s="108"/>
+      <c r="L7" s="108"/>
+      <c r="M7" s="108"/>
+      <c r="N7" s="108"/>
+      <c r="O7" s="108"/>
     </row>
     <row r="9" spans="1:17">
-      <c r="I9" s="96" t="s">
-        <v>99</v>
-      </c>
-      <c r="J9" s="96"/>
-      <c r="K9" s="96"/>
-      <c r="L9" s="96"/>
-      <c r="M9" s="96"/>
-      <c r="N9" s="96"/>
-      <c r="O9" s="96"/>
-      <c r="P9" s="96"/>
-      <c r="Q9" s="96"/>
+      <c r="I9" s="102" t="s">
+        <v>97</v>
+      </c>
+      <c r="J9" s="102"/>
+      <c r="K9" s="102"/>
+      <c r="L9" s="102"/>
+      <c r="M9" s="102"/>
+      <c r="N9" s="102"/>
+      <c r="O9" s="102"/>
+      <c r="P9" s="102"/>
+      <c r="Q9" s="102"/>
     </row>
     <row r="10" spans="1:17">
-      <c r="I10" s="96"/>
-      <c r="J10" s="96"/>
-      <c r="K10" s="96"/>
-      <c r="L10" s="96"/>
-      <c r="M10" s="96"/>
-      <c r="N10" s="96"/>
-      <c r="O10" s="96"/>
-      <c r="P10" s="96"/>
-      <c r="Q10" s="96"/>
+      <c r="I10" s="102"/>
+      <c r="J10" s="102"/>
+      <c r="K10" s="102"/>
+      <c r="L10" s="102"/>
+      <c r="M10" s="102"/>
+      <c r="N10" s="102"/>
+      <c r="O10" s="102"/>
+      <c r="P10" s="102"/>
+      <c r="Q10" s="102"/>
     </row>
     <row r="11" spans="1:17">
-      <c r="I11" s="96"/>
-      <c r="J11" s="96"/>
-      <c r="K11" s="96"/>
-      <c r="L11" s="96"/>
-      <c r="M11" s="96"/>
-      <c r="N11" s="96"/>
-      <c r="O11" s="96"/>
-      <c r="P11" s="96"/>
-      <c r="Q11" s="96"/>
+      <c r="I11" s="102"/>
+      <c r="J11" s="102"/>
+      <c r="K11" s="102"/>
+      <c r="L11" s="102"/>
+      <c r="M11" s="102"/>
+      <c r="N11" s="102"/>
+      <c r="O11" s="102"/>
+      <c r="P11" s="102"/>
+      <c r="Q11" s="102"/>
     </row>
     <row r="12" spans="1:17">
-      <c r="I12" s="96"/>
-      <c r="J12" s="96"/>
-      <c r="K12" s="96"/>
-      <c r="L12" s="96"/>
-      <c r="M12" s="96"/>
-      <c r="N12" s="96"/>
-      <c r="O12" s="96"/>
-      <c r="P12" s="96"/>
-      <c r="Q12" s="96"/>
+      <c r="I12" s="102"/>
+      <c r="J12" s="102"/>
+      <c r="K12" s="102"/>
+      <c r="L12" s="102"/>
+      <c r="M12" s="102"/>
+      <c r="N12" s="102"/>
+      <c r="O12" s="102"/>
+      <c r="P12" s="102"/>
+      <c r="Q12" s="102"/>
     </row>
     <row r="13" spans="1:17">
-      <c r="I13" s="96"/>
-      <c r="J13" s="96"/>
-      <c r="K13" s="96"/>
-      <c r="L13" s="96"/>
-      <c r="M13" s="96"/>
-      <c r="N13" s="96"/>
-      <c r="O13" s="96"/>
-      <c r="P13" s="96"/>
-      <c r="Q13" s="96"/>
+      <c r="I13" s="102"/>
+      <c r="J13" s="102"/>
+      <c r="K13" s="102"/>
+      <c r="L13" s="102"/>
+      <c r="M13" s="102"/>
+      <c r="N13" s="102"/>
+      <c r="O13" s="102"/>
+      <c r="P13" s="102"/>
+      <c r="Q13" s="102"/>
     </row>
     <row r="14" spans="1:17">
-      <c r="I14" s="96"/>
-      <c r="J14" s="96"/>
-      <c r="K14" s="96"/>
-      <c r="L14" s="96"/>
-      <c r="M14" s="96"/>
-      <c r="N14" s="96"/>
-      <c r="O14" s="96"/>
-      <c r="P14" s="96"/>
-      <c r="Q14" s="96"/>
+      <c r="I14" s="102"/>
+      <c r="J14" s="102"/>
+      <c r="K14" s="102"/>
+      <c r="L14" s="102"/>
+      <c r="M14" s="102"/>
+      <c r="N14" s="102"/>
+      <c r="O14" s="102"/>
+      <c r="P14" s="102"/>
+      <c r="Q14" s="102"/>
     </row>
     <row r="15" spans="1:17">
-      <c r="I15" s="96"/>
-      <c r="J15" s="96"/>
-      <c r="K15" s="96"/>
-      <c r="L15" s="96"/>
-      <c r="M15" s="96"/>
-      <c r="N15" s="96"/>
-      <c r="O15" s="96"/>
-      <c r="P15" s="96"/>
-      <c r="Q15" s="96"/>
+      <c r="I15" s="102"/>
+      <c r="J15" s="102"/>
+      <c r="K15" s="102"/>
+      <c r="L15" s="102"/>
+      <c r="M15" s="102"/>
+      <c r="N15" s="102"/>
+      <c r="O15" s="102"/>
+      <c r="P15" s="102"/>
+      <c r="Q15" s="102"/>
     </row>
     <row r="17" spans="3:17" ht="15.75">
       <c r="I17" s="11" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="3:17">
-      <c r="I18" s="92" t="s">
-        <v>100</v>
-      </c>
-      <c r="J18" s="92"/>
-      <c r="K18" s="92"/>
-      <c r="L18" s="92"/>
-      <c r="M18" s="92"/>
-      <c r="N18" s="92"/>
-      <c r="O18" s="92"/>
-      <c r="P18" s="92"/>
-      <c r="Q18" s="92"/>
+      <c r="I18" s="88" t="s">
+        <v>98</v>
+      </c>
+      <c r="J18" s="88"/>
+      <c r="K18" s="88"/>
+      <c r="L18" s="88"/>
+      <c r="M18" s="88"/>
+      <c r="N18" s="88"/>
+      <c r="O18" s="88"/>
+      <c r="P18" s="88"/>
+      <c r="Q18" s="88"/>
     </row>
     <row r="19" spans="3:17">
-      <c r="I19" s="92"/>
-      <c r="J19" s="92"/>
-      <c r="K19" s="92"/>
-      <c r="L19" s="92"/>
-      <c r="M19" s="92"/>
-      <c r="N19" s="92"/>
-      <c r="O19" s="92"/>
-      <c r="P19" s="92"/>
-      <c r="Q19" s="92"/>
+      <c r="I19" s="88"/>
+      <c r="J19" s="88"/>
+      <c r="K19" s="88"/>
+      <c r="L19" s="88"/>
+      <c r="M19" s="88"/>
+      <c r="N19" s="88"/>
+      <c r="O19" s="88"/>
+      <c r="P19" s="88"/>
+      <c r="Q19" s="88"/>
     </row>
     <row r="20" spans="3:17">
-      <c r="I20" s="92"/>
-      <c r="J20" s="92"/>
-      <c r="K20" s="92"/>
-      <c r="L20" s="92"/>
-      <c r="M20" s="92"/>
-      <c r="N20" s="92"/>
-      <c r="O20" s="92"/>
-      <c r="P20" s="92"/>
-      <c r="Q20" s="92"/>
+      <c r="I20" s="88"/>
+      <c r="J20" s="88"/>
+      <c r="K20" s="88"/>
+      <c r="L20" s="88"/>
+      <c r="M20" s="88"/>
+      <c r="N20" s="88"/>
+      <c r="O20" s="88"/>
+      <c r="P20" s="88"/>
+      <c r="Q20" s="88"/>
     </row>
     <row r="21" spans="3:17">
-      <c r="I21" s="92"/>
-      <c r="J21" s="92"/>
-      <c r="K21" s="92"/>
-      <c r="L21" s="92"/>
-      <c r="M21" s="92"/>
-      <c r="N21" s="92"/>
-      <c r="O21" s="92"/>
-      <c r="P21" s="92"/>
-      <c r="Q21" s="92"/>
+      <c r="I21" s="88"/>
+      <c r="J21" s="88"/>
+      <c r="K21" s="88"/>
+      <c r="L21" s="88"/>
+      <c r="M21" s="88"/>
+      <c r="N21" s="88"/>
+      <c r="O21" s="88"/>
+      <c r="P21" s="88"/>
+      <c r="Q21" s="88"/>
     </row>
     <row r="22" spans="3:17">
-      <c r="I22" s="92"/>
-      <c r="J22" s="92"/>
-      <c r="K22" s="92"/>
-      <c r="L22" s="92"/>
-      <c r="M22" s="92"/>
-      <c r="N22" s="92"/>
-      <c r="O22" s="92"/>
-      <c r="P22" s="92"/>
-      <c r="Q22" s="92"/>
+      <c r="I22" s="88"/>
+      <c r="J22" s="88"/>
+      <c r="K22" s="88"/>
+      <c r="L22" s="88"/>
+      <c r="M22" s="88"/>
+      <c r="N22" s="88"/>
+      <c r="O22" s="88"/>
+      <c r="P22" s="88"/>
+      <c r="Q22" s="88"/>
     </row>
     <row r="23" spans="3:17">
-      <c r="I23" s="92"/>
-      <c r="J23" s="92"/>
-      <c r="K23" s="92"/>
-      <c r="L23" s="92"/>
-      <c r="M23" s="92"/>
-      <c r="N23" s="92"/>
-      <c r="O23" s="92"/>
-      <c r="P23" s="92"/>
-      <c r="Q23" s="92"/>
+      <c r="I23" s="88"/>
+      <c r="J23" s="88"/>
+      <c r="K23" s="88"/>
+      <c r="L23" s="88"/>
+      <c r="M23" s="88"/>
+      <c r="N23" s="88"/>
+      <c r="O23" s="88"/>
+      <c r="P23" s="88"/>
+      <c r="Q23" s="88"/>
     </row>
     <row r="24" spans="3:17">
-      <c r="I24" s="92"/>
-      <c r="J24" s="92"/>
-      <c r="K24" s="92"/>
-      <c r="L24" s="92"/>
-      <c r="M24" s="92"/>
-      <c r="N24" s="92"/>
-      <c r="O24" s="92"/>
-      <c r="P24" s="92"/>
-      <c r="Q24" s="92"/>
+      <c r="I24" s="88"/>
+      <c r="J24" s="88"/>
+      <c r="K24" s="88"/>
+      <c r="L24" s="88"/>
+      <c r="M24" s="88"/>
+      <c r="N24" s="88"/>
+      <c r="O24" s="88"/>
+      <c r="P24" s="88"/>
+      <c r="Q24" s="88"/>
     </row>
     <row r="25" spans="3:17">
-      <c r="I25" s="92"/>
-      <c r="J25" s="92"/>
-      <c r="K25" s="92"/>
-      <c r="L25" s="92"/>
-      <c r="M25" s="92"/>
-      <c r="N25" s="92"/>
-      <c r="O25" s="92"/>
-      <c r="P25" s="92"/>
-      <c r="Q25" s="92"/>
+      <c r="I25" s="88"/>
+      <c r="J25" s="88"/>
+      <c r="K25" s="88"/>
+      <c r="L25" s="88"/>
+      <c r="M25" s="88"/>
+      <c r="N25" s="88"/>
+      <c r="O25" s="88"/>
+      <c r="P25" s="88"/>
+      <c r="Q25" s="88"/>
     </row>
     <row r="30" spans="3:17">
       <c r="C30" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="3:17">
       <c r="C31" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32" spans="3:17">
       <c r="C32" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="3:14">
       <c r="C33" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="35" spans="3:14" ht="18.75">
+      <c r="C35" s="105" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="35" spans="3:14" ht="18.75">
-      <c r="C35" s="128" t="s">
+      <c r="D35" s="106"/>
+      <c r="E35" s="106"/>
+      <c r="F35" s="106"/>
+      <c r="G35" s="106"/>
+      <c r="H35" s="107"/>
+      <c r="I35" s="103" t="s">
+        <v>193</v>
+      </c>
+      <c r="J35" s="103"/>
+      <c r="K35" s="103"/>
+      <c r="L35" s="103"/>
+      <c r="M35" s="103"/>
+      <c r="N35" s="103"/>
+    </row>
+    <row r="36" spans="3:14">
+      <c r="C36" s="83" t="s">
+        <v>105</v>
+      </c>
+      <c r="D36" s="83"/>
+      <c r="E36" s="83"/>
+      <c r="F36" s="83"/>
+      <c r="G36" s="83"/>
+      <c r="H36" s="83"/>
+      <c r="I36" s="8" t="s">
         <v>106</v>
-      </c>
-      <c r="D35" s="129"/>
-      <c r="E35" s="129"/>
-      <c r="F35" s="129"/>
-      <c r="G35" s="129"/>
-      <c r="H35" s="130"/>
-      <c r="I35" s="97" t="s">
-        <v>195</v>
-      </c>
-      <c r="J35" s="97"/>
-      <c r="K35" s="97"/>
-      <c r="L35" s="97"/>
-      <c r="M35" s="97"/>
-      <c r="N35" s="97"/>
-    </row>
-    <row r="36" spans="3:14">
-      <c r="C36" s="71" t="s">
-        <v>107</v>
-      </c>
-      <c r="D36" s="71"/>
-      <c r="E36" s="71"/>
-      <c r="F36" s="71"/>
-      <c r="G36" s="71"/>
-      <c r="H36" s="71"/>
-      <c r="I36" s="8" t="s">
-        <v>108</v>
       </c>
       <c r="J36" s="8"/>
       <c r="K36" s="8"/>
@@ -7305,7 +7558,7 @@
     </row>
     <row r="37" spans="3:14" ht="15" customHeight="1">
       <c r="C37" s="104" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D37" s="104"/>
       <c r="E37" s="104"/>
@@ -7313,7 +7566,7 @@
       <c r="G37" s="104"/>
       <c r="H37" s="104"/>
       <c r="I37" s="104" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J37" s="104"/>
       <c r="K37" s="104"/>
@@ -7379,7 +7632,7 @@
     </row>
     <row r="42" spans="3:14">
       <c r="C42" s="104" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D42" s="104"/>
       <c r="E42" s="104"/>
@@ -7387,7 +7640,7 @@
       <c r="G42" s="104"/>
       <c r="H42" s="104"/>
       <c r="I42" s="104" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J42" s="104"/>
       <c r="K42" s="104"/>
@@ -7411,7 +7664,7 @@
     </row>
     <row r="44" spans="3:14">
       <c r="C44" s="104" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D44" s="104"/>
       <c r="E44" s="104"/>
@@ -7419,7 +7672,7 @@
       <c r="G44" s="104"/>
       <c r="H44" s="104"/>
       <c r="I44" s="104" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="J44" s="104"/>
       <c r="K44" s="104"/>
@@ -7442,16 +7695,16 @@
       <c r="N45" s="104"/>
     </row>
     <row r="46" spans="3:14">
-      <c r="C46" s="67" t="s">
-        <v>115</v>
-      </c>
-      <c r="D46" s="68"/>
-      <c r="E46" s="68"/>
-      <c r="F46" s="68"/>
-      <c r="G46" s="68"/>
-      <c r="H46" s="69"/>
+      <c r="C46" s="60" t="s">
+        <v>113</v>
+      </c>
+      <c r="D46" s="61"/>
+      <c r="E46" s="61"/>
+      <c r="F46" s="61"/>
+      <c r="G46" s="61"/>
+      <c r="H46" s="62"/>
       <c r="I46" s="8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J46" s="8"/>
       <c r="K46" s="8"/>
@@ -7460,73 +7713,73 @@
       <c r="N46" s="8"/>
     </row>
     <row r="47" spans="3:14" ht="15" customHeight="1">
-      <c r="C47" s="98" t="s">
-        <v>117</v>
-      </c>
-      <c r="D47" s="99"/>
-      <c r="E47" s="99"/>
-      <c r="F47" s="99"/>
-      <c r="G47" s="99"/>
-      <c r="H47" s="100"/>
-      <c r="I47" s="98" t="s">
-        <v>118</v>
-      </c>
-      <c r="J47" s="99"/>
-      <c r="K47" s="99"/>
-      <c r="L47" s="99"/>
-      <c r="M47" s="99"/>
-      <c r="N47" s="100"/>
+      <c r="C47" s="109" t="s">
+        <v>115</v>
+      </c>
+      <c r="D47" s="110"/>
+      <c r="E47" s="110"/>
+      <c r="F47" s="110"/>
+      <c r="G47" s="110"/>
+      <c r="H47" s="111"/>
+      <c r="I47" s="109" t="s">
+        <v>116</v>
+      </c>
+      <c r="J47" s="110"/>
+      <c r="K47" s="110"/>
+      <c r="L47" s="110"/>
+      <c r="M47" s="110"/>
+      <c r="N47" s="111"/>
     </row>
     <row r="48" spans="3:14">
-      <c r="C48" s="101"/>
-      <c r="D48" s="102"/>
-      <c r="E48" s="102"/>
-      <c r="F48" s="102"/>
-      <c r="G48" s="102"/>
-      <c r="H48" s="103"/>
-      <c r="I48" s="101"/>
-      <c r="J48" s="102"/>
-      <c r="K48" s="102"/>
-      <c r="L48" s="102"/>
-      <c r="M48" s="102"/>
-      <c r="N48" s="103"/>
+      <c r="C48" s="112"/>
+      <c r="D48" s="113"/>
+      <c r="E48" s="113"/>
+      <c r="F48" s="113"/>
+      <c r="G48" s="113"/>
+      <c r="H48" s="114"/>
+      <c r="I48" s="112"/>
+      <c r="J48" s="113"/>
+      <c r="K48" s="113"/>
+      <c r="L48" s="113"/>
+      <c r="M48" s="113"/>
+      <c r="N48" s="114"/>
     </row>
     <row r="50" spans="2:14" ht="15.75">
       <c r="B50" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="51" spans="2:14">
       <c r="C51" s="18" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="52" spans="2:14">
       <c r="C52" s="18" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="53" spans="2:14">
       <c r="C53" s="25" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="54" spans="2:14">
       <c r="C54" s="18" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="55" spans="2:14">
       <c r="C55" s="18" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="56" spans="2:14">
       <c r="C56" s="18" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="57" spans="2:14">
@@ -7534,52 +7787,52 @@
     </row>
     <row r="58" spans="2:14">
       <c r="C58" s="18" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="59" spans="2:14" ht="15" customHeight="1">
-      <c r="C59" s="96" t="s">
-        <v>193</v>
-      </c>
-      <c r="D59" s="96"/>
-      <c r="E59" s="96"/>
-      <c r="F59" s="96"/>
-      <c r="G59" s="96"/>
-      <c r="H59" s="96"/>
-      <c r="I59" s="96"/>
-      <c r="J59" s="96"/>
-      <c r="K59" s="96"/>
-      <c r="L59" s="96"/>
-      <c r="M59" s="96"/>
-      <c r="N59" s="96"/>
+      <c r="C59" s="102" t="s">
+        <v>191</v>
+      </c>
+      <c r="D59" s="102"/>
+      <c r="E59" s="102"/>
+      <c r="F59" s="102"/>
+      <c r="G59" s="102"/>
+      <c r="H59" s="102"/>
+      <c r="I59" s="102"/>
+      <c r="J59" s="102"/>
+      <c r="K59" s="102"/>
+      <c r="L59" s="102"/>
+      <c r="M59" s="102"/>
+      <c r="N59" s="102"/>
     </row>
     <row r="60" spans="2:14">
-      <c r="C60" s="96"/>
-      <c r="D60" s="96"/>
-      <c r="E60" s="96"/>
-      <c r="F60" s="96"/>
-      <c r="G60" s="96"/>
-      <c r="H60" s="96"/>
-      <c r="I60" s="96"/>
-      <c r="J60" s="96"/>
-      <c r="K60" s="96"/>
-      <c r="L60" s="96"/>
-      <c r="M60" s="96"/>
-      <c r="N60" s="96"/>
+      <c r="C60" s="102"/>
+      <c r="D60" s="102"/>
+      <c r="E60" s="102"/>
+      <c r="F60" s="102"/>
+      <c r="G60" s="102"/>
+      <c r="H60" s="102"/>
+      <c r="I60" s="102"/>
+      <c r="J60" s="102"/>
+      <c r="K60" s="102"/>
+      <c r="L60" s="102"/>
+      <c r="M60" s="102"/>
+      <c r="N60" s="102"/>
     </row>
     <row r="61" spans="2:14">
-      <c r="C61" s="96"/>
-      <c r="D61" s="96"/>
-      <c r="E61" s="96"/>
-      <c r="F61" s="96"/>
-      <c r="G61" s="96"/>
-      <c r="H61" s="96"/>
-      <c r="I61" s="96"/>
-      <c r="J61" s="96"/>
-      <c r="K61" s="96"/>
-      <c r="L61" s="96"/>
-      <c r="M61" s="96"/>
-      <c r="N61" s="96"/>
+      <c r="C61" s="102"/>
+      <c r="D61" s="102"/>
+      <c r="E61" s="102"/>
+      <c r="F61" s="102"/>
+      <c r="G61" s="102"/>
+      <c r="H61" s="102"/>
+      <c r="I61" s="102"/>
+      <c r="J61" s="102"/>
+      <c r="K61" s="102"/>
+      <c r="L61" s="102"/>
+      <c r="M61" s="102"/>
+      <c r="N61" s="102"/>
     </row>
     <row r="62" spans="2:14">
       <c r="C62" s="3"/>
@@ -7597,37 +7850,21 @@
     </row>
     <row r="63" spans="2:14" ht="15.75">
       <c r="C63" s="26" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="64" spans="2:14">
       <c r="C64" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="65" spans="3:3">
       <c r="C65" s="13" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="C59:N61"/>
-    <mergeCell ref="I35:N35"/>
-    <mergeCell ref="C36:H36"/>
-    <mergeCell ref="C37:H41"/>
-    <mergeCell ref="I37:N41"/>
-    <mergeCell ref="C35:H35"/>
     <mergeCell ref="D5:O7"/>
     <mergeCell ref="I9:Q15"/>
     <mergeCell ref="I18:Q25"/>
@@ -7638,6 +7875,22 @@
     <mergeCell ref="C42:H43"/>
     <mergeCell ref="I42:N43"/>
     <mergeCell ref="C46:H46"/>
+    <mergeCell ref="C59:N61"/>
+    <mergeCell ref="I35:N35"/>
+    <mergeCell ref="C36:H36"/>
+    <mergeCell ref="C37:H41"/>
+    <mergeCell ref="I37:N41"/>
+    <mergeCell ref="C35:H35"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:O2"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Summary!A1" display="Summary" xr:uid="{EB5C04DC-2059-40C4-9BA2-9B4CFB0444C8}"/>
@@ -7648,191 +7901,198 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="13" max="13" width="4.85546875" customWidth="1"/>
+    <col min="14" max="14" width="5.85546875" customWidth="1"/>
+    <col min="15" max="15" width="4.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" thickBot="1">
       <c r="A1" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="117" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="99" t="s">
+        <v>217</v>
+      </c>
+      <c r="C1" s="100"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="52" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1" s="99" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1" s="100"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="86" t="s">
+        <v>210</v>
+      </c>
+      <c r="J1" s="87"/>
+      <c r="K1" s="99" t="s">
         <v>219</v>
       </c>
-      <c r="C1" s="118"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="52" t="s">
-        <v>288</v>
-      </c>
-      <c r="F1" s="117" t="s">
+      <c r="L1" s="101"/>
+      <c r="M1" s="85">
+        <v>45931</v>
+      </c>
+      <c r="N1" s="85"/>
+      <c r="O1" s="85"/>
+    </row>
+    <row r="2" spans="1:15" ht="15.75" thickBot="1">
+      <c r="B2" s="99" t="s">
         <v>220</v>
       </c>
-      <c r="G1" s="118"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="115" t="s">
-        <v>212</v>
-      </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="117" t="s">
-        <v>221</v>
-      </c>
-      <c r="L1" s="119"/>
-      <c r="M1" s="115">
-        <v>45750</v>
-      </c>
-      <c r="N1" s="116"/>
-    </row>
-    <row r="2" spans="1:15" ht="15.75" thickBot="1">
-      <c r="B2" s="117" t="s">
-        <v>222</v>
-      </c>
-      <c r="C2" s="118"/>
-      <c r="D2" s="119"/>
+      <c r="C2" s="100"/>
+      <c r="D2" s="101"/>
       <c r="E2" s="53">
         <v>0</v>
       </c>
-      <c r="F2" s="117" t="s">
-        <v>223</v>
-      </c>
-      <c r="G2" s="118"/>
-      <c r="H2" s="119"/>
-      <c r="I2" s="115" t="s">
-        <v>212</v>
-      </c>
-      <c r="J2" s="116"/>
-      <c r="K2" s="117" t="s">
-        <v>224</v>
-      </c>
-      <c r="L2" s="119"/>
-      <c r="M2" s="115">
-        <v>45750</v>
-      </c>
-      <c r="N2" s="116"/>
+      <c r="F2" s="99" t="s">
+        <v>221</v>
+      </c>
+      <c r="G2" s="100"/>
+      <c r="H2" s="101"/>
+      <c r="I2" s="86" t="s">
+        <v>210</v>
+      </c>
+      <c r="J2" s="87"/>
+      <c r="K2" s="99" t="s">
+        <v>222</v>
+      </c>
+      <c r="L2" s="101"/>
+      <c r="M2" s="85">
+        <v>45968</v>
+      </c>
+      <c r="N2" s="85"/>
+      <c r="O2" s="85"/>
     </row>
     <row r="4" spans="1:15">
       <c r="C4" s="5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="15" customHeight="1">
-      <c r="C5" s="96" t="s">
-        <v>162</v>
-      </c>
-      <c r="D5" s="96"/>
-      <c r="E5" s="96"/>
-      <c r="F5" s="96"/>
-      <c r="G5" s="96"/>
-      <c r="H5" s="96"/>
-      <c r="I5" s="96"/>
-      <c r="J5" s="96"/>
-      <c r="K5" s="96"/>
-      <c r="L5" s="96"/>
-      <c r="M5" s="96"/>
-      <c r="N5" s="96"/>
-      <c r="O5" s="96"/>
+      <c r="C5" s="102" t="s">
+        <v>160</v>
+      </c>
+      <c r="D5" s="102"/>
+      <c r="E5" s="102"/>
+      <c r="F5" s="102"/>
+      <c r="G5" s="102"/>
+      <c r="H5" s="102"/>
+      <c r="I5" s="102"/>
+      <c r="J5" s="102"/>
+      <c r="K5" s="102"/>
+      <c r="L5" s="102"/>
+      <c r="M5" s="102"/>
+      <c r="N5" s="102"/>
+      <c r="O5" s="102"/>
     </row>
     <row r="6" spans="1:15">
-      <c r="C6" s="96"/>
-      <c r="D6" s="96"/>
-      <c r="E6" s="96"/>
-      <c r="F6" s="96"/>
-      <c r="G6" s="96"/>
-      <c r="H6" s="96"/>
-      <c r="I6" s="96"/>
-      <c r="J6" s="96"/>
-      <c r="K6" s="96"/>
-      <c r="L6" s="96"/>
-      <c r="M6" s="96"/>
-      <c r="N6" s="96"/>
-      <c r="O6" s="96"/>
+      <c r="C6" s="102"/>
+      <c r="D6" s="102"/>
+      <c r="E6" s="102"/>
+      <c r="F6" s="102"/>
+      <c r="G6" s="102"/>
+      <c r="H6" s="102"/>
+      <c r="I6" s="102"/>
+      <c r="J6" s="102"/>
+      <c r="K6" s="102"/>
+      <c r="L6" s="102"/>
+      <c r="M6" s="102"/>
+      <c r="N6" s="102"/>
+      <c r="O6" s="102"/>
     </row>
     <row r="7" spans="1:15">
-      <c r="C7" s="96"/>
-      <c r="D7" s="96"/>
-      <c r="E7" s="96"/>
-      <c r="F7" s="96"/>
-      <c r="G7" s="96"/>
-      <c r="H7" s="96"/>
-      <c r="I7" s="96"/>
-      <c r="J7" s="96"/>
-      <c r="K7" s="96"/>
-      <c r="L7" s="96"/>
-      <c r="M7" s="96"/>
-      <c r="N7" s="96"/>
-      <c r="O7" s="96"/>
+      <c r="C7" s="102"/>
+      <c r="D7" s="102"/>
+      <c r="E7" s="102"/>
+      <c r="F7" s="102"/>
+      <c r="G7" s="102"/>
+      <c r="H7" s="102"/>
+      <c r="I7" s="102"/>
+      <c r="J7" s="102"/>
+      <c r="K7" s="102"/>
+      <c r="L7" s="102"/>
+      <c r="M7" s="102"/>
+      <c r="N7" s="102"/>
+      <c r="O7" s="102"/>
     </row>
     <row r="8" spans="1:15">
-      <c r="C8" s="96"/>
-      <c r="D8" s="96"/>
-      <c r="E8" s="96"/>
-      <c r="F8" s="96"/>
-      <c r="G8" s="96"/>
-      <c r="H8" s="96"/>
-      <c r="I8" s="96"/>
-      <c r="J8" s="96"/>
-      <c r="K8" s="96"/>
-      <c r="L8" s="96"/>
-      <c r="M8" s="96"/>
-      <c r="N8" s="96"/>
-      <c r="O8" s="96"/>
+      <c r="C8" s="102"/>
+      <c r="D8" s="102"/>
+      <c r="E8" s="102"/>
+      <c r="F8" s="102"/>
+      <c r="G8" s="102"/>
+      <c r="H8" s="102"/>
+      <c r="I8" s="102"/>
+      <c r="J8" s="102"/>
+      <c r="K8" s="102"/>
+      <c r="L8" s="102"/>
+      <c r="M8" s="102"/>
+      <c r="N8" s="102"/>
+      <c r="O8" s="102"/>
     </row>
     <row r="10" spans="1:15">
-      <c r="B10" t="s">
-        <v>168</v>
+      <c r="B10" s="5" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="B11" s="18" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="B12" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="B13" s="18" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" spans="1:15">
       <c r="B14" s="18" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="15" spans="1:15">
       <c r="B15" s="18" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="B16" s="18" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="18" spans="13:16">
-      <c r="M18" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="18" spans="13:17">
+      <c r="M18" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="19" spans="13:17">
+      <c r="Q19" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="20" spans="13:17">
+      <c r="Q20" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="21" spans="13:17">
+      <c r="Q21" t="s">
         <v>163</v>
-      </c>
-      <c r="P18" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="19" spans="13:16">
-      <c r="P19" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="20" spans="13:16">
-      <c r="P20" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="21" spans="13:16">
-      <c r="P21" t="s">
-        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -7842,12 +8102,12 @@
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="K1:L1"/>
-    <mergeCell ref="M1:N1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="M2:O2"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Summary!A1" display="Summary" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
@@ -7857,76 +8117,79 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:J53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="83.85546875" customWidth="1"/>
-    <col min="3" max="3" width="82.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" customWidth="1"/>
-    <col min="5" max="5" width="18.28515625" customWidth="1"/>
-    <col min="6" max="6" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.85546875" customWidth="1"/>
+    <col min="2" max="2" width="59.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.28515625" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" thickBot="1">
-      <c r="B1" s="126" t="s">
+    <row r="1" spans="1:9" ht="30.75" thickBot="1">
+      <c r="A1" s="54" t="s">
+        <v>217</v>
+      </c>
+      <c r="B1" s="52" t="s">
+        <v>285</v>
+      </c>
+      <c r="C1" s="54" t="s">
+        <v>218</v>
+      </c>
+      <c r="D1" s="48" t="s">
+        <v>210</v>
+      </c>
+      <c r="E1" s="99" t="s">
         <v>219</v>
       </c>
-      <c r="C1" s="52" t="s">
-        <v>288</v>
-      </c>
-      <c r="D1" s="126" t="s">
+      <c r="F1" s="101"/>
+      <c r="G1" s="85">
+        <v>45931</v>
+      </c>
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
+    </row>
+    <row r="2" spans="1:9" ht="15.75" thickBot="1">
+      <c r="A2" s="54" t="s">
         <v>220</v>
       </c>
-      <c r="E1" s="115" t="s">
-        <v>212</v>
-      </c>
-      <c r="F1" s="116"/>
-      <c r="G1" s="117" t="s">
+      <c r="B2" s="53">
+        <v>0</v>
+      </c>
+      <c r="C2" s="54" t="s">
         <v>221</v>
       </c>
-      <c r="H1" s="119"/>
-      <c r="I1" s="115">
-        <v>45750</v>
-      </c>
-      <c r="J1" s="116"/>
-    </row>
-    <row r="2" spans="1:10" ht="15.75" thickBot="1">
-      <c r="B2" s="126" t="s">
+      <c r="D2" s="48" t="s">
+        <v>210</v>
+      </c>
+      <c r="E2" s="99" t="s">
         <v>222</v>
       </c>
-      <c r="C2" s="53">
-        <v>0</v>
-      </c>
-      <c r="D2" s="126" t="s">
-        <v>223</v>
-      </c>
-      <c r="E2" s="115" t="s">
-        <v>212</v>
-      </c>
-      <c r="F2" s="116"/>
-      <c r="G2" s="117" t="s">
-        <v>224</v>
-      </c>
-      <c r="H2" s="119"/>
-      <c r="I2" s="115">
-        <v>45750</v>
-      </c>
-      <c r="J2" s="116"/>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="F2" s="101"/>
+      <c r="G2" s="85">
+        <v>45968</v>
+      </c>
+      <c r="H2" s="85"/>
+      <c r="I2" s="85"/>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="15" customHeight="1">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15" customHeight="1">
       <c r="A6" s="12"/>
-      <c r="B6" s="96" t="s">
-        <v>160</v>
+      <c r="B6" s="102" t="s">
+        <v>158</v>
       </c>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
@@ -7934,304 +8197,348 @@
       <c r="F6" s="17"/>
       <c r="G6" s="17"/>
       <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-    </row>
-    <row r="7" spans="1:10">
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="12"/>
-      <c r="B7" s="96"/>
+      <c r="B7" s="102"/>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
       <c r="F7" s="17"/>
       <c r="G7" s="17"/>
       <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-    </row>
-    <row r="8" spans="1:10">
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="12"/>
-      <c r="B8" s="96"/>
+      <c r="B8" s="102"/>
       <c r="C8" s="17"/>
       <c r="D8" s="17"/>
       <c r="E8" s="17"/>
       <c r="F8" s="17"/>
       <c r="G8" s="17"/>
       <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-    </row>
-    <row r="9" spans="1:10">
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="12"/>
-      <c r="B9" s="96"/>
+      <c r="B9" s="102"/>
       <c r="C9" s="17"/>
       <c r="D9" s="17"/>
       <c r="E9" s="17"/>
       <c r="F9" s="17"/>
       <c r="G9" s="17"/>
       <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-    </row>
-    <row r="10" spans="1:10">
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="12"/>
-      <c r="B10" s="96"/>
-    </row>
-    <row r="12" spans="1:10" ht="15" customHeight="1">
-      <c r="B12" s="92" t="s">
+      <c r="B10" s="102"/>
+    </row>
+    <row r="12" spans="1:9" ht="15" customHeight="1">
+      <c r="B12" s="88" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="B13" s="88"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="B14" s="88"/>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="B15" s="3"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="B16" s="3"/>
+    </row>
+    <row r="17" spans="2:10">
+      <c r="B17" s="3"/>
+    </row>
+    <row r="18" spans="2:10" ht="15" customHeight="1">
+      <c r="B18" s="102" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10">
+      <c r="B19" s="102"/>
+    </row>
+    <row r="20" spans="2:10">
+      <c r="B20" s="102"/>
+    </row>
+    <row r="21" spans="2:10">
+      <c r="B21" s="102"/>
+    </row>
+    <row r="22" spans="2:10">
+      <c r="B22" s="102"/>
+    </row>
+    <row r="24" spans="2:10" ht="15" customHeight="1">
+      <c r="B24" s="88" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10">
+      <c r="B25" s="88"/>
+    </row>
+    <row r="26" spans="2:10">
+      <c r="B26" s="88"/>
+    </row>
+    <row r="28" spans="2:10">
+      <c r="B28" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C28" s="134" t="s">
+        <v>119</v>
+      </c>
+      <c r="D28" s="134"/>
+      <c r="E28" s="134"/>
+      <c r="F28" s="134"/>
+      <c r="G28" s="134"/>
+      <c r="H28" s="134"/>
+      <c r="I28" s="134"/>
+      <c r="J28" s="134"/>
+    </row>
+    <row r="29" spans="2:10">
+      <c r="B29" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C29" s="139" t="s">
+        <v>121</v>
+      </c>
+      <c r="D29" s="139"/>
+      <c r="E29" s="139"/>
+      <c r="F29" s="139"/>
+      <c r="G29" s="139"/>
+      <c r="H29" s="139"/>
+      <c r="I29" s="139"/>
+      <c r="J29" s="139"/>
+    </row>
+    <row r="30" spans="2:10">
+      <c r="B30" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="C30" s="139" t="s">
+        <v>123</v>
+      </c>
+      <c r="D30" s="139"/>
+      <c r="E30" s="139"/>
+      <c r="F30" s="139"/>
+      <c r="G30" s="139"/>
+      <c r="H30" s="139"/>
+      <c r="I30" s="139"/>
+      <c r="J30" s="139"/>
+    </row>
+    <row r="31" spans="2:10" ht="30">
+      <c r="B31" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="C31" s="139" t="s">
+        <v>125</v>
+      </c>
+      <c r="D31" s="139"/>
+      <c r="E31" s="139"/>
+      <c r="F31" s="139"/>
+      <c r="G31" s="139"/>
+      <c r="H31" s="139"/>
+      <c r="I31" s="139"/>
+      <c r="J31" s="139"/>
+    </row>
+    <row r="32" spans="2:10" ht="28.5" customHeight="1">
+      <c r="B32" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C32" s="140" t="s">
+        <v>127</v>
+      </c>
+      <c r="D32" s="140"/>
+      <c r="E32" s="140"/>
+      <c r="F32" s="140"/>
+      <c r="G32" s="140"/>
+      <c r="H32" s="140"/>
+      <c r="I32" s="140"/>
+      <c r="J32" s="140"/>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="C33" s="137"/>
+      <c r="D33" s="138"/>
+      <c r="E33" s="138"/>
+      <c r="F33" s="138"/>
+      <c r="G33" s="138"/>
+      <c r="H33" s="138"/>
+      <c r="I33" s="138"/>
+      <c r="J33" s="138"/>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="B34" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
-      <c r="B13" s="92"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="B14" s="92"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="B15" s="3"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="B16" s="3"/>
-    </row>
-    <row r="17" spans="2:3">
-      <c r="B17" s="3"/>
-    </row>
-    <row r="18" spans="2:3" ht="15" customHeight="1">
-      <c r="B18" s="96" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3">
-      <c r="B19" s="96"/>
-    </row>
-    <row r="20" spans="2:3">
-      <c r="B20" s="96"/>
-    </row>
-    <row r="21" spans="2:3">
-      <c r="B21" s="96"/>
-    </row>
-    <row r="22" spans="2:3">
-      <c r="B22" s="96"/>
-    </row>
-    <row r="24" spans="2:3" ht="15" customHeight="1">
-      <c r="B24" s="92" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3">
-      <c r="B25" s="92"/>
-    </row>
-    <row r="26" spans="2:3">
-      <c r="B26" s="92"/>
-    </row>
-    <row r="28" spans="2:3">
-      <c r="B28" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="29" spans="2:3">
-      <c r="B29" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="30" spans="2:3">
-      <c r="B30" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="31" spans="2:3" ht="30">
-      <c r="B31" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="32" spans="2:3">
-      <c r="B32" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="34" spans="2:5">
-      <c r="B34" t="s">
+    <row r="35" spans="1:10">
+      <c r="B35" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="35" spans="2:5">
-      <c r="B35" t="s">
+    <row r="37" spans="1:10">
+      <c r="B37" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="B38" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="37" spans="2:5">
-      <c r="B37" t="s">
+    <row r="39" spans="1:10" ht="15" customHeight="1">
+      <c r="B39" s="121" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="38" spans="2:5">
-      <c r="B38" t="s">
+      <c r="C39" s="121"/>
+      <c r="D39" s="121"/>
+      <c r="E39" s="121"/>
+    </row>
+    <row r="40" spans="1:10" ht="15" customHeight="1">
+      <c r="A40" s="122" t="s">
+        <v>156</v>
+      </c>
+      <c r="B40" s="124" t="s">
+        <v>132</v>
+      </c>
+      <c r="C40" s="124" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="15" customHeight="1">
+      <c r="A41" s="123"/>
+      <c r="B41" s="124"/>
+      <c r="C41" s="124"/>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="115" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="39" spans="2:5" ht="15" customHeight="1">
-      <c r="B39" s="110" t="s">
+      <c r="B42" s="104" t="s">
+        <v>143</v>
+      </c>
+      <c r="C42" s="117" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="116"/>
+      <c r="B43" s="104"/>
+      <c r="C43" s="117"/>
+    </row>
+    <row r="44" spans="1:10" ht="45">
+      <c r="A44" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="C39" s="110"/>
-      <c r="D39" s="110"/>
-      <c r="E39" s="110"/>
-    </row>
-    <row r="40" spans="2:5" ht="15" customHeight="1">
-      <c r="B40" s="111" t="s">
-        <v>158</v>
-      </c>
-      <c r="C40" s="113" t="s">
-        <v>134</v>
-      </c>
-      <c r="D40" s="113" t="s">
+      <c r="B44" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="15" customHeight="1">
+      <c r="A45" s="115" t="s">
+        <v>140</v>
+      </c>
+      <c r="B45" s="104" t="s">
+        <v>148</v>
+      </c>
+      <c r="C45" s="104" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="116"/>
+      <c r="B46" s="104"/>
+      <c r="C46" s="104"/>
+    </row>
+    <row r="47" spans="1:10" ht="15" customHeight="1">
+      <c r="A47" s="115" t="s">
+        <v>139</v>
+      </c>
+      <c r="B47" s="104" t="s">
+        <v>150</v>
+      </c>
+      <c r="C47" s="104" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="118"/>
+      <c r="B48" s="104"/>
+      <c r="C48" s="104"/>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="116"/>
+      <c r="B49" s="104"/>
+      <c r="C49" s="104"/>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="119" t="s">
+        <v>141</v>
+      </c>
+      <c r="B50" s="104" t="s">
+        <v>152</v>
+      </c>
+      <c r="C50" s="104" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="120"/>
+      <c r="B51" s="104"/>
+      <c r="C51" s="104"/>
+    </row>
+    <row r="52" spans="1:3" ht="30" customHeight="1">
+      <c r="A52" s="115" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="41" spans="2:5" ht="15" customHeight="1">
-      <c r="B41" s="112"/>
-      <c r="C41" s="113"/>
-      <c r="D41" s="113"/>
-    </row>
-    <row r="42" spans="2:5">
-      <c r="B42" s="105" t="s">
-        <v>139</v>
-      </c>
-      <c r="C42" s="104" t="s">
-        <v>145</v>
-      </c>
-      <c r="D42" s="114" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="43" spans="2:5">
-      <c r="B43" s="107"/>
-      <c r="C43" s="104"/>
-      <c r="D43" s="114"/>
-    </row>
-    <row r="44" spans="2:5" ht="30">
-      <c r="B44" s="16" t="s">
-        <v>140</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="45" spans="2:5" ht="15" customHeight="1">
-      <c r="B45" s="105" t="s">
-        <v>142</v>
-      </c>
-      <c r="C45" s="104" t="s">
-        <v>150</v>
-      </c>
-      <c r="D45" s="104" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="46" spans="2:5">
-      <c r="B46" s="107"/>
-      <c r="C46" s="104"/>
-      <c r="D46" s="104"/>
-    </row>
-    <row r="47" spans="2:5" ht="15" customHeight="1">
-      <c r="B47" s="105" t="s">
-        <v>141</v>
-      </c>
-      <c r="C47" s="104" t="s">
-        <v>152</v>
-      </c>
-      <c r="D47" s="104" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="48" spans="2:5">
-      <c r="B48" s="106"/>
-      <c r="C48" s="104"/>
-      <c r="D48" s="104"/>
-    </row>
-    <row r="49" spans="2:4">
-      <c r="B49" s="107"/>
-      <c r="C49" s="104"/>
-      <c r="D49" s="104"/>
-    </row>
-    <row r="50" spans="2:4">
-      <c r="B50" s="108" t="s">
-        <v>143</v>
-      </c>
-      <c r="C50" s="104" t="s">
+      <c r="B52" s="104" t="s">
         <v>154</v>
       </c>
-      <c r="D50" s="104" t="s">
+      <c r="C52" s="104" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="51" spans="2:4">
-      <c r="B51" s="109"/>
-      <c r="C51" s="104"/>
-      <c r="D51" s="104"/>
-    </row>
-    <row r="52" spans="2:4" ht="30" customHeight="1">
-      <c r="B52" s="105" t="s">
-        <v>146</v>
-      </c>
-      <c r="C52" s="114" t="s">
-        <v>156</v>
-      </c>
-      <c r="D52" s="114" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="53" spans="2:4">
-      <c r="B53" s="107"/>
-      <c r="C53" s="114"/>
-      <c r="D53" s="114"/>
+    <row r="53" spans="1:3">
+      <c r="A53" s="116"/>
+      <c r="B53" s="104"/>
+      <c r="C53" s="104"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="C47:C49"/>
-    <mergeCell ref="D47:D49"/>
+  <mergeCells count="32">
+    <mergeCell ref="C28:J28"/>
+    <mergeCell ref="C29:J29"/>
+    <mergeCell ref="C30:J30"/>
+    <mergeCell ref="C31:J31"/>
+    <mergeCell ref="C32:J32"/>
+    <mergeCell ref="B6:B10"/>
+    <mergeCell ref="A47:A49"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="A50:A51"/>
     <mergeCell ref="B42:B43"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="B6:B10"/>
-    <mergeCell ref="B47:B49"/>
-    <mergeCell ref="B52:B53"/>
     <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="C50:C51"/>
     <mergeCell ref="B18:B22"/>
     <mergeCell ref="B12:B14"/>
     <mergeCell ref="B24:B26"/>
     <mergeCell ref="B39:E39"/>
+    <mergeCell ref="A40:A41"/>
     <mergeCell ref="B40:B41"/>
     <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="B52:B53"/>
     <mergeCell ref="C52:C53"/>
-    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="B47:B49"/>
+    <mergeCell ref="C47:C49"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="G2:I2"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A5" location="Summary!A1" display="Summary" xr:uid="{00000000-0004-0000-0700-000000000000}"/>
@@ -8240,169 +8547,4 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:Q37"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:17" ht="15.75" thickBot="1">
-      <c r="A1" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="117" t="s">
-        <v>219</v>
-      </c>
-      <c r="C1" s="118"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="120" t="s">
-        <v>259</v>
-      </c>
-      <c r="F1" s="121"/>
-      <c r="G1" s="117" t="s">
-        <v>220</v>
-      </c>
-      <c r="H1" s="118"/>
-      <c r="I1" s="118"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="115" t="s">
-        <v>212</v>
-      </c>
-      <c r="L1" s="122"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="117" t="s">
-        <v>221</v>
-      </c>
-      <c r="O1" s="119"/>
-      <c r="P1" s="115">
-        <v>45750</v>
-      </c>
-      <c r="Q1" s="116"/>
-    </row>
-    <row r="2" spans="1:17" ht="15.75" thickBot="1">
-      <c r="B2" s="117" t="s">
-        <v>222</v>
-      </c>
-      <c r="C2" s="118"/>
-      <c r="D2" s="119"/>
-      <c r="E2" s="123">
-        <v>0</v>
-      </c>
-      <c r="F2" s="124"/>
-      <c r="G2" s="117" t="s">
-        <v>223</v>
-      </c>
-      <c r="H2" s="118"/>
-      <c r="I2" s="118"/>
-      <c r="J2" s="119"/>
-      <c r="K2" s="115" t="s">
-        <v>212</v>
-      </c>
-      <c r="L2" s="122"/>
-      <c r="M2" s="116"/>
-      <c r="N2" s="117" t="s">
-        <v>224</v>
-      </c>
-      <c r="O2" s="119"/>
-      <c r="P2" s="115">
-        <v>45019</v>
-      </c>
-      <c r="Q2" s="116"/>
-    </row>
-    <row r="4" spans="1:17">
-      <c r="B4" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17">
-      <c r="B5" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17">
-      <c r="B6" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3">
-      <c r="C24" s="12"/>
-    </row>
-    <row r="25" spans="2:3">
-      <c r="B25" t="s">
-        <v>226</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="26" spans="2:3">
-      <c r="C26" s="12" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3">
-      <c r="C28" s="45" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="29" spans="2:3">
-      <c r="C29" s="45" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="30" spans="2:3">
-      <c r="C30" s="45"/>
-    </row>
-    <row r="31" spans="2:3">
-      <c r="C31" s="45" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="32" spans="2:3">
-      <c r="C32" s="45"/>
-    </row>
-    <row r="33" spans="3:3">
-      <c r="C33" s="45" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="34" spans="3:3">
-      <c r="C34" s="45"/>
-    </row>
-    <row r="35" spans="3:3">
-      <c r="C35" s="45" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="36" spans="3:3">
-      <c r="C36" s="45"/>
-    </row>
-    <row r="37" spans="3:3">
-      <c r="C37" s="45"/>
-    </row>
-  </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:M1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="N2:O2"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="C25" r:id="rId1" xr:uid="{00000000-0004-0000-0800-000000000000}"/>
-    <hyperlink ref="C26" r:id="rId2" xr:uid="{00000000-0004-0000-0800-000001000000}"/>
-    <hyperlink ref="A1" location="Summary!A1" display="Summary" xr:uid="{00000000-0004-0000-0800-000004000000}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId3"/>
-  <drawing r:id="rId4"/>
-</worksheet>
 </file>